--- a/results/round1/model_error_analysis.xlsx
+++ b/results/round1/model_error_analysis.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/04e7a7c5f324bc23/Documents/Master/Term 2/CPSC532/Assignment 2/RAG_concept_net/results/round1/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="19" documentId="8_{9B80AE2F-DA47-4317-A80D-090BB33B2025}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6263D55D-5AD0-45DC-A828-D2583F8FF31A}"/>
+  <xr:revisionPtr revIDLastSave="398" documentId="8_{9B80AE2F-DA47-4317-A80D-090BB33B2025}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3C161911-32B2-48FB-9BB8-9DF7D3F07182}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{CE51F1D6-FCDF-4133-8196-27B2E7D5A517}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="6867" uniqueCount="993">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8393" uniqueCount="993">
   <si>
     <t>question</t>
   </si>
@@ -5391,12 +5391,12 @@
     </filterColumn>
     <filterColumn colId="6">
       <filters>
-        <filter val="1"/>
+        <filter val="8"/>
       </filters>
     </filterColumn>
     <filterColumn colId="7">
       <filters>
-        <filter val="rag"/>
+        <filter val="rag_optional"/>
       </filters>
     </filterColumn>
   </autoFilter>
@@ -19269,7 +19269,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="449" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="449" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A449" t="s">
         <v>53</v>
       </c>
@@ -19301,7 +19301,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="450" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="450" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A450" t="s">
         <v>65</v>
       </c>
@@ -19333,7 +19333,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="451" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="451" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A451" t="s">
         <v>57</v>
       </c>
@@ -19365,7 +19365,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="452" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="452" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A452" t="s">
         <v>49</v>
       </c>
@@ -19397,7 +19397,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="453" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="453" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A453" t="s">
         <v>51</v>
       </c>
@@ -19429,7 +19429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="454" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="454" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A454" t="s">
         <v>92</v>
       </c>
@@ -19461,7 +19461,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="455" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="455" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A455" t="s">
         <v>67</v>
       </c>
@@ -19493,7 +19493,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="456" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="456" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A456" t="s">
         <v>55</v>
       </c>
@@ -19525,7 +19525,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="457" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="457" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A457" t="s">
         <v>59</v>
       </c>
@@ -19557,7 +19557,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="458" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="458" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A458" t="s">
         <v>560</v>
       </c>
@@ -19589,7 +19589,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="459" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="459" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A459" t="s">
         <v>219</v>
       </c>
@@ -19621,7 +19621,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="460" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="460" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A460" t="s">
         <v>42</v>
       </c>
@@ -19653,7 +19653,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="461" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="461" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A461" t="s">
         <v>45</v>
       </c>
@@ -19685,7 +19685,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="462" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="462" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A462" t="s">
         <v>61</v>
       </c>
@@ -19717,7 +19717,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="463" spans="1:10" x14ac:dyDescent="0.45">
+    <row r="463" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
       <c r="A463" t="s">
         <v>63</v>
       </c>
@@ -32421,7 +32421,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="860" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="860" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A860" t="s">
         <v>581</v>
       </c>
@@ -32453,7 +32453,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="861" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="861" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A861" t="s">
         <v>569</v>
       </c>
@@ -32485,7 +32485,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="862" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="862" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A862" t="s">
         <v>61</v>
       </c>
@@ -32517,7 +32517,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="863" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="863" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A863" t="s">
         <v>59</v>
       </c>
@@ -32549,7 +32549,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="864" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="864" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A864" t="s">
         <v>53</v>
       </c>
@@ -32581,7 +32581,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="865" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="865" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A865" t="s">
         <v>49</v>
       </c>
@@ -32613,7 +32613,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="866" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="866" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A866" t="s">
         <v>63</v>
       </c>
@@ -32645,7 +32645,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="867" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="867" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A867" t="s">
         <v>45</v>
       </c>
@@ -32677,7 +32677,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="868" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="868" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A868" t="s">
         <v>57</v>
       </c>
@@ -32709,7 +32709,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="869" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="869" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A869" t="s">
         <v>219</v>
       </c>
@@ -32741,7 +32741,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="870" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="870" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A870" t="s">
         <v>187</v>
       </c>
@@ -32773,7 +32773,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="871" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="871" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A871" t="s">
         <v>587</v>
       </c>
@@ -32805,7 +32805,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="872" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="872" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A872" t="s">
         <v>649</v>
       </c>
@@ -32837,7 +32837,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="873" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="873" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A873" t="s">
         <v>92</v>
       </c>
@@ -32869,7 +32869,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="874" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="874" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A874" t="s">
         <v>65</v>
       </c>
@@ -32901,7 +32901,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="875" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="875" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A875" t="s">
         <v>67</v>
       </c>
@@ -32933,7 +32933,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="876" spans="1:10" hidden="1" x14ac:dyDescent="0.45">
+    <row r="876" spans="1:10" x14ac:dyDescent="0.45">
       <c r="A876" t="s">
         <v>51</v>
       </c>
@@ -33703,11 +33703,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EC951338-5A47-4C7D-924F-81EEEAE91B18}">
-  <dimension ref="A1:K84"/>
+  <dimension ref="A1:K302"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="62.19921875" customWidth="1"/>
     <col min="3" max="3" width="24" customWidth="1"/>
+    <col min="13" max="13" width="8.9296875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" x14ac:dyDescent="0.45">
@@ -33858,7 +33859,7 @@
         <v>0</v>
       </c>
       <c r="K5">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.45">
@@ -33945,7 +33946,7 @@
         <v>0</v>
       </c>
       <c r="K8">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.45">
@@ -34067,7 +34068,7 @@
         <v>0</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.45">
@@ -34099,7 +34100,7 @@
         <v>0</v>
       </c>
       <c r="K13">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.45">
@@ -34326,7 +34327,7 @@
         <v>0</v>
       </c>
       <c r="K20">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.45">
@@ -34734,7 +34735,7 @@
         <v>0</v>
       </c>
       <c r="K32">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.45">
@@ -35051,7 +35052,7 @@
         <v>0</v>
       </c>
       <c r="K42">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.45">
@@ -35167,7 +35168,7 @@
         <v>0</v>
       </c>
       <c r="K46">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.45">
@@ -36086,7 +36087,7 @@
         <v>0</v>
       </c>
       <c r="K75">
-        <v>0</v>
+        <v>4</v>
       </c>
     </row>
     <row r="76" spans="1:11" x14ac:dyDescent="0.45">
@@ -36401,6 +36402,7324 @@
         <v>0</v>
       </c>
       <c r="K84">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A85" t="s">
+        <v>47</v>
+      </c>
+      <c r="B85" t="s">
+        <v>19</v>
+      </c>
+      <c r="C85" t="s">
+        <v>853</v>
+      </c>
+      <c r="D85" t="s">
+        <v>13</v>
+      </c>
+      <c r="E85" t="b">
+        <v>0</v>
+      </c>
+      <c r="F85" t="s">
+        <v>44</v>
+      </c>
+      <c r="G85">
+        <v>1</v>
+      </c>
+      <c r="H85" t="s">
+        <v>682</v>
+      </c>
+      <c r="I85" t="s">
+        <v>683</v>
+      </c>
+      <c r="J85">
+        <v>0</v>
+      </c>
+      <c r="K85">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="86" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A86" t="s">
+        <v>57</v>
+      </c>
+      <c r="B86" t="s">
+        <v>11</v>
+      </c>
+      <c r="C86" t="s">
+        <v>854</v>
+      </c>
+      <c r="D86" t="s">
+        <v>13</v>
+      </c>
+      <c r="E86" t="b">
+        <v>0</v>
+      </c>
+      <c r="F86" t="s">
+        <v>44</v>
+      </c>
+      <c r="G86">
+        <v>1</v>
+      </c>
+      <c r="H86" t="s">
+        <v>682</v>
+      </c>
+      <c r="I86" t="s">
+        <v>683</v>
+      </c>
+      <c r="J86">
+        <v>0</v>
+      </c>
+      <c r="K86">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="87" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A87" t="s">
+        <v>560</v>
+      </c>
+      <c r="B87" t="s">
+        <v>19</v>
+      </c>
+      <c r="C87" t="s">
+        <v>855</v>
+      </c>
+      <c r="D87" t="s">
+        <v>24</v>
+      </c>
+      <c r="E87" t="b">
+        <v>0</v>
+      </c>
+      <c r="F87" t="s">
+        <v>44</v>
+      </c>
+      <c r="G87">
+        <v>1</v>
+      </c>
+      <c r="H87" t="s">
+        <v>682</v>
+      </c>
+      <c r="I87" t="s">
+        <v>683</v>
+      </c>
+      <c r="J87">
+        <v>0</v>
+      </c>
+      <c r="K87">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="88" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A88" t="s">
+        <v>49</v>
+      </c>
+      <c r="B88" t="s">
+        <v>19</v>
+      </c>
+      <c r="C88" t="s">
+        <v>856</v>
+      </c>
+      <c r="D88" t="s">
+        <v>24</v>
+      </c>
+      <c r="E88" t="b">
+        <v>0</v>
+      </c>
+      <c r="F88" t="s">
+        <v>44</v>
+      </c>
+      <c r="G88">
+        <v>1</v>
+      </c>
+      <c r="H88" t="s">
+        <v>682</v>
+      </c>
+      <c r="I88" t="s">
+        <v>683</v>
+      </c>
+      <c r="J88">
+        <v>0</v>
+      </c>
+      <c r="K88">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="89" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A89" t="s">
+        <v>53</v>
+      </c>
+      <c r="B89" t="s">
+        <v>11</v>
+      </c>
+      <c r="C89" t="s">
+        <v>857</v>
+      </c>
+      <c r="D89" t="s">
+        <v>24</v>
+      </c>
+      <c r="E89" t="b">
+        <v>0</v>
+      </c>
+      <c r="F89" t="s">
+        <v>44</v>
+      </c>
+      <c r="G89">
+        <v>1</v>
+      </c>
+      <c r="H89" t="s">
+        <v>682</v>
+      </c>
+      <c r="I89" t="s">
+        <v>683</v>
+      </c>
+      <c r="J89">
+        <v>0</v>
+      </c>
+      <c r="K89">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A90" t="s">
+        <v>45</v>
+      </c>
+      <c r="B90" t="s">
+        <v>19</v>
+      </c>
+      <c r="C90" t="s">
+        <v>858</v>
+      </c>
+      <c r="D90" t="s">
+        <v>13</v>
+      </c>
+      <c r="E90" t="b">
+        <v>0</v>
+      </c>
+      <c r="F90" t="s">
+        <v>44</v>
+      </c>
+      <c r="G90">
+        <v>1</v>
+      </c>
+      <c r="H90" t="s">
+        <v>682</v>
+      </c>
+      <c r="I90" t="s">
+        <v>683</v>
+      </c>
+      <c r="J90">
+        <v>0</v>
+      </c>
+      <c r="K90">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="91" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A91" t="s">
+        <v>63</v>
+      </c>
+      <c r="B91" t="s">
+        <v>11</v>
+      </c>
+      <c r="C91" t="s">
+        <v>859</v>
+      </c>
+      <c r="D91" t="s">
+        <v>13</v>
+      </c>
+      <c r="E91" t="b">
+        <v>0</v>
+      </c>
+      <c r="F91" t="s">
+        <v>44</v>
+      </c>
+      <c r="G91">
+        <v>1</v>
+      </c>
+      <c r="H91" t="s">
+        <v>682</v>
+      </c>
+      <c r="I91" t="s">
+        <v>683</v>
+      </c>
+      <c r="J91">
+        <v>0</v>
+      </c>
+      <c r="K91">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="92" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A92" t="s">
+        <v>65</v>
+      </c>
+      <c r="B92" t="s">
+        <v>11</v>
+      </c>
+      <c r="C92" t="s">
+        <v>860</v>
+      </c>
+      <c r="D92" t="s">
+        <v>13</v>
+      </c>
+      <c r="E92" t="b">
+        <v>0</v>
+      </c>
+      <c r="F92" t="s">
+        <v>44</v>
+      </c>
+      <c r="G92">
+        <v>1</v>
+      </c>
+      <c r="H92" t="s">
+        <v>682</v>
+      </c>
+      <c r="I92" t="s">
+        <v>683</v>
+      </c>
+      <c r="J92">
+        <v>0</v>
+      </c>
+      <c r="K92">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="93" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A93" t="s">
+        <v>55</v>
+      </c>
+      <c r="B93" t="s">
+        <v>24</v>
+      </c>
+      <c r="C93" t="s">
+        <v>861</v>
+      </c>
+      <c r="D93" t="s">
+        <v>19</v>
+      </c>
+      <c r="E93" t="b">
+        <v>0</v>
+      </c>
+      <c r="F93" t="s">
+        <v>44</v>
+      </c>
+      <c r="G93">
+        <v>1</v>
+      </c>
+      <c r="H93" t="s">
+        <v>682</v>
+      </c>
+      <c r="I93" t="s">
+        <v>683</v>
+      </c>
+      <c r="J93">
+        <v>0</v>
+      </c>
+      <c r="K93">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="94" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A94" t="s">
+        <v>219</v>
+      </c>
+      <c r="B94" t="s">
+        <v>11</v>
+      </c>
+      <c r="C94" t="s">
+        <v>862</v>
+      </c>
+      <c r="D94" t="s">
+        <v>13</v>
+      </c>
+      <c r="E94" t="b">
+        <v>0</v>
+      </c>
+      <c r="F94" t="s">
+        <v>44</v>
+      </c>
+      <c r="G94">
+        <v>1</v>
+      </c>
+      <c r="H94" t="s">
+        <v>682</v>
+      </c>
+      <c r="I94" t="s">
+        <v>683</v>
+      </c>
+      <c r="J94">
+        <v>0</v>
+      </c>
+      <c r="K94">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="95" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A95" t="s">
+        <v>59</v>
+      </c>
+      <c r="B95" t="s">
+        <v>11</v>
+      </c>
+      <c r="C95" t="s">
+        <v>863</v>
+      </c>
+      <c r="D95" t="s">
+        <v>13</v>
+      </c>
+      <c r="E95" t="b">
+        <v>0</v>
+      </c>
+      <c r="F95" t="s">
+        <v>44</v>
+      </c>
+      <c r="G95">
+        <v>1</v>
+      </c>
+      <c r="H95" t="s">
+        <v>682</v>
+      </c>
+      <c r="I95" t="s">
+        <v>683</v>
+      </c>
+      <c r="J95">
+        <v>0</v>
+      </c>
+      <c r="K95">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="96" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A96" t="s">
+        <v>61</v>
+      </c>
+      <c r="B96" t="s">
+        <v>19</v>
+      </c>
+      <c r="C96" t="s">
+        <v>864</v>
+      </c>
+      <c r="D96" t="s">
+        <v>24</v>
+      </c>
+      <c r="E96" t="b">
+        <v>0</v>
+      </c>
+      <c r="F96" t="s">
+        <v>44</v>
+      </c>
+      <c r="G96">
+        <v>1</v>
+      </c>
+      <c r="H96" t="s">
+        <v>682</v>
+      </c>
+      <c r="I96" t="s">
+        <v>683</v>
+      </c>
+      <c r="J96">
+        <v>0</v>
+      </c>
+      <c r="K96">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="97" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A97" t="s">
+        <v>865</v>
+      </c>
+      <c r="B97" t="s">
+        <v>24</v>
+      </c>
+      <c r="C97" t="s">
+        <v>866</v>
+      </c>
+      <c r="D97" t="s">
+        <v>11</v>
+      </c>
+      <c r="E97" t="b">
+        <v>0</v>
+      </c>
+      <c r="F97" t="s">
+        <v>44</v>
+      </c>
+      <c r="G97">
+        <v>1</v>
+      </c>
+      <c r="H97" t="s">
+        <v>682</v>
+      </c>
+      <c r="I97" t="s">
+        <v>683</v>
+      </c>
+      <c r="J97">
+        <v>0</v>
+      </c>
+      <c r="K97">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="98" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A98" t="s">
+        <v>92</v>
+      </c>
+      <c r="B98" t="s">
+        <v>19</v>
+      </c>
+      <c r="C98" t="s">
+        <v>867</v>
+      </c>
+      <c r="D98" t="s">
+        <v>13</v>
+      </c>
+      <c r="E98" t="b">
+        <v>0</v>
+      </c>
+      <c r="F98" t="s">
+        <v>44</v>
+      </c>
+      <c r="G98">
+        <v>1</v>
+      </c>
+      <c r="H98" t="s">
+        <v>682</v>
+      </c>
+      <c r="I98" t="s">
+        <v>683</v>
+      </c>
+      <c r="J98">
+        <v>0</v>
+      </c>
+      <c r="K98">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="99" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A99" t="s">
+        <v>42</v>
+      </c>
+      <c r="B99" t="s">
+        <v>19</v>
+      </c>
+      <c r="C99" t="s">
+        <v>868</v>
+      </c>
+      <c r="D99" t="s">
+        <v>13</v>
+      </c>
+      <c r="E99" t="b">
+        <v>0</v>
+      </c>
+      <c r="F99" t="s">
+        <v>44</v>
+      </c>
+      <c r="G99">
+        <v>1</v>
+      </c>
+      <c r="H99" t="s">
+        <v>682</v>
+      </c>
+      <c r="I99" t="s">
+        <v>683</v>
+      </c>
+      <c r="J99">
+        <v>0</v>
+      </c>
+      <c r="K99">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="100" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A100" t="s">
+        <v>67</v>
+      </c>
+      <c r="B100" t="s">
+        <v>19</v>
+      </c>
+      <c r="C100" t="s">
+        <v>869</v>
+      </c>
+      <c r="D100" t="s">
+        <v>13</v>
+      </c>
+      <c r="E100" t="b">
+        <v>0</v>
+      </c>
+      <c r="F100" t="s">
+        <v>44</v>
+      </c>
+      <c r="G100">
+        <v>1</v>
+      </c>
+      <c r="H100" t="s">
+        <v>682</v>
+      </c>
+      <c r="I100" t="s">
+        <v>683</v>
+      </c>
+      <c r="J100">
+        <v>0</v>
+      </c>
+      <c r="K100">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="101" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A101" t="s">
+        <v>51</v>
+      </c>
+      <c r="B101" t="s">
+        <v>11</v>
+      </c>
+      <c r="C101" t="s">
+        <v>870</v>
+      </c>
+      <c r="D101" t="s">
+        <v>13</v>
+      </c>
+      <c r="E101" t="b">
+        <v>0</v>
+      </c>
+      <c r="F101" t="s">
+        <v>44</v>
+      </c>
+      <c r="G101">
+        <v>1</v>
+      </c>
+      <c r="H101" t="s">
+        <v>682</v>
+      </c>
+      <c r="I101" t="s">
+        <v>683</v>
+      </c>
+      <c r="J101">
+        <v>0</v>
+      </c>
+      <c r="K101">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="102" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A102" t="s">
+        <v>480</v>
+      </c>
+      <c r="B102" t="s">
+        <v>11</v>
+      </c>
+      <c r="C102" t="s">
+        <v>681</v>
+      </c>
+      <c r="D102" t="s">
+        <v>19</v>
+      </c>
+      <c r="E102" t="b">
+        <v>0</v>
+      </c>
+      <c r="F102" t="s">
+        <v>14</v>
+      </c>
+      <c r="G102">
+        <v>1</v>
+      </c>
+      <c r="H102" t="s">
+        <v>682</v>
+      </c>
+      <c r="I102" t="s">
+        <v>683</v>
+      </c>
+      <c r="J102">
+        <v>0</v>
+      </c>
+      <c r="K102">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="103" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A103" t="s">
+        <v>10</v>
+      </c>
+      <c r="B103" t="s">
+        <v>11</v>
+      </c>
+      <c r="C103" t="s">
+        <v>684</v>
+      </c>
+      <c r="D103" t="s">
+        <v>13</v>
+      </c>
+      <c r="E103" t="b">
+        <v>0</v>
+      </c>
+      <c r="F103" t="s">
+        <v>14</v>
+      </c>
+      <c r="G103">
+        <v>1</v>
+      </c>
+      <c r="H103" t="s">
+        <v>682</v>
+      </c>
+      <c r="I103" t="s">
+        <v>683</v>
+      </c>
+      <c r="J103">
+        <v>0</v>
+      </c>
+      <c r="K103">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A104" t="s">
+        <v>17</v>
+      </c>
+      <c r="B104" t="s">
+        <v>24</v>
+      </c>
+      <c r="C104" t="s">
+        <v>685</v>
+      </c>
+      <c r="D104" t="s">
+        <v>19</v>
+      </c>
+      <c r="E104" t="b">
+        <v>0</v>
+      </c>
+      <c r="F104" t="s">
+        <v>14</v>
+      </c>
+      <c r="G104">
+        <v>1</v>
+      </c>
+      <c r="H104" t="s">
+        <v>682</v>
+      </c>
+      <c r="I104" t="s">
+        <v>683</v>
+      </c>
+      <c r="J104">
+        <v>0</v>
+      </c>
+      <c r="K104">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="105" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A105" t="s">
+        <v>33</v>
+      </c>
+      <c r="B105" t="s">
+        <v>11</v>
+      </c>
+      <c r="C105" t="s">
+        <v>686</v>
+      </c>
+      <c r="D105" t="s">
+        <v>13</v>
+      </c>
+      <c r="E105" t="b">
+        <v>0</v>
+      </c>
+      <c r="F105" t="s">
+        <v>14</v>
+      </c>
+      <c r="G105">
+        <v>1</v>
+      </c>
+      <c r="H105" t="s">
+        <v>682</v>
+      </c>
+      <c r="I105" t="s">
+        <v>683</v>
+      </c>
+      <c r="J105">
+        <v>0</v>
+      </c>
+      <c r="K105">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A106" t="s">
+        <v>20</v>
+      </c>
+      <c r="B106" t="s">
+        <v>11</v>
+      </c>
+      <c r="C106" t="s">
+        <v>687</v>
+      </c>
+      <c r="D106" t="s">
+        <v>19</v>
+      </c>
+      <c r="E106" t="b">
+        <v>0</v>
+      </c>
+      <c r="F106" t="s">
+        <v>14</v>
+      </c>
+      <c r="G106">
+        <v>1</v>
+      </c>
+      <c r="H106" t="s">
+        <v>682</v>
+      </c>
+      <c r="I106" t="s">
+        <v>683</v>
+      </c>
+      <c r="J106">
+        <v>0</v>
+      </c>
+      <c r="K106">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="107" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A107" t="s">
+        <v>27</v>
+      </c>
+      <c r="B107" t="s">
+        <v>19</v>
+      </c>
+      <c r="C107" t="s">
+        <v>688</v>
+      </c>
+      <c r="D107" t="s">
+        <v>11</v>
+      </c>
+      <c r="E107" t="b">
+        <v>0</v>
+      </c>
+      <c r="F107" t="s">
+        <v>14</v>
+      </c>
+      <c r="G107">
+        <v>1</v>
+      </c>
+      <c r="H107" t="s">
+        <v>682</v>
+      </c>
+      <c r="I107" t="s">
+        <v>683</v>
+      </c>
+      <c r="J107">
+        <v>0</v>
+      </c>
+      <c r="K107">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="108" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A108" t="s">
+        <v>353</v>
+      </c>
+      <c r="B108" t="s">
+        <v>24</v>
+      </c>
+      <c r="C108" t="s">
+        <v>689</v>
+      </c>
+      <c r="D108" t="s">
+        <v>19</v>
+      </c>
+      <c r="E108" t="b">
+        <v>0</v>
+      </c>
+      <c r="F108" t="s">
+        <v>14</v>
+      </c>
+      <c r="G108">
+        <v>1</v>
+      </c>
+      <c r="H108" t="s">
+        <v>682</v>
+      </c>
+      <c r="I108" t="s">
+        <v>683</v>
+      </c>
+      <c r="J108">
+        <v>0</v>
+      </c>
+      <c r="K108">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="109" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A109" t="s">
+        <v>77</v>
+      </c>
+      <c r="B109" t="s">
+        <v>13</v>
+      </c>
+      <c r="C109" t="s">
+        <v>690</v>
+      </c>
+      <c r="D109" t="s">
+        <v>19</v>
+      </c>
+      <c r="E109" t="b">
+        <v>0</v>
+      </c>
+      <c r="F109" t="s">
+        <v>14</v>
+      </c>
+      <c r="G109">
+        <v>1</v>
+      </c>
+      <c r="H109" t="s">
+        <v>682</v>
+      </c>
+      <c r="I109" t="s">
+        <v>683</v>
+      </c>
+      <c r="J109">
+        <v>0</v>
+      </c>
+      <c r="K109">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="110" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A110" t="s">
+        <v>29</v>
+      </c>
+      <c r="B110" t="s">
+        <v>13</v>
+      </c>
+      <c r="C110" t="s">
+        <v>691</v>
+      </c>
+      <c r="D110" t="s">
+        <v>11</v>
+      </c>
+      <c r="E110" t="b">
+        <v>0</v>
+      </c>
+      <c r="F110" t="s">
+        <v>14</v>
+      </c>
+      <c r="G110">
+        <v>1</v>
+      </c>
+      <c r="H110" t="s">
+        <v>682</v>
+      </c>
+      <c r="I110" t="s">
+        <v>683</v>
+      </c>
+      <c r="J110">
+        <v>0</v>
+      </c>
+      <c r="K110">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="111" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A111" t="s">
+        <v>368</v>
+      </c>
+      <c r="B111" t="s">
+        <v>24</v>
+      </c>
+      <c r="C111" t="s">
+        <v>692</v>
+      </c>
+      <c r="D111" t="s">
+        <v>11</v>
+      </c>
+      <c r="E111" t="b">
+        <v>0</v>
+      </c>
+      <c r="F111" t="s">
+        <v>14</v>
+      </c>
+      <c r="G111">
+        <v>1</v>
+      </c>
+      <c r="H111" t="s">
+        <v>682</v>
+      </c>
+      <c r="I111" t="s">
+        <v>683</v>
+      </c>
+      <c r="J111">
+        <v>0</v>
+      </c>
+      <c r="K111">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="112" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A112" t="s">
+        <v>31</v>
+      </c>
+      <c r="B112" t="s">
+        <v>24</v>
+      </c>
+      <c r="C112" t="s">
+        <v>358</v>
+      </c>
+      <c r="D112" t="s">
+        <v>19</v>
+      </c>
+      <c r="E112" t="b">
+        <v>0</v>
+      </c>
+      <c r="F112" t="s">
+        <v>14</v>
+      </c>
+      <c r="G112">
+        <v>1</v>
+      </c>
+      <c r="H112" t="s">
+        <v>682</v>
+      </c>
+      <c r="I112" t="s">
+        <v>683</v>
+      </c>
+      <c r="J112">
+        <v>0</v>
+      </c>
+      <c r="K112">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="113" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A113" t="s">
+        <v>396</v>
+      </c>
+      <c r="B113" t="s">
+        <v>24</v>
+      </c>
+      <c r="C113" t="s">
+        <v>693</v>
+      </c>
+      <c r="D113" t="s">
+        <v>13</v>
+      </c>
+      <c r="E113" t="b">
+        <v>0</v>
+      </c>
+      <c r="F113" t="s">
+        <v>14</v>
+      </c>
+      <c r="G113">
+        <v>1</v>
+      </c>
+      <c r="H113" t="s">
+        <v>682</v>
+      </c>
+      <c r="I113" t="s">
+        <v>683</v>
+      </c>
+      <c r="J113">
+        <v>0</v>
+      </c>
+      <c r="K113">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="114" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A114" t="s">
+        <v>38</v>
+      </c>
+      <c r="B114" t="s">
+        <v>24</v>
+      </c>
+      <c r="C114" t="s">
+        <v>836</v>
+      </c>
+      <c r="D114" t="s">
+        <v>13</v>
+      </c>
+      <c r="E114" t="b">
+        <v>0</v>
+      </c>
+      <c r="F114" t="s">
+        <v>37</v>
+      </c>
+      <c r="G114">
+        <v>1</v>
+      </c>
+      <c r="H114" t="s">
+        <v>682</v>
+      </c>
+      <c r="I114" t="s">
+        <v>683</v>
+      </c>
+      <c r="J114">
+        <v>0</v>
+      </c>
+      <c r="K114">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="115" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A115" t="s">
+        <v>837</v>
+      </c>
+      <c r="B115" t="s">
+        <v>167</v>
+      </c>
+      <c r="C115" t="s">
+        <v>168</v>
+      </c>
+      <c r="D115" t="s">
+        <v>24</v>
+      </c>
+      <c r="E115" t="b">
+        <v>0</v>
+      </c>
+      <c r="F115" t="s">
+        <v>37</v>
+      </c>
+      <c r="G115">
+        <v>1</v>
+      </c>
+      <c r="H115" t="s">
+        <v>682</v>
+      </c>
+      <c r="I115" t="s">
+        <v>683</v>
+      </c>
+      <c r="J115">
+        <v>0</v>
+      </c>
+      <c r="K115">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="116" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A116" t="s">
+        <v>535</v>
+      </c>
+      <c r="B116" t="s">
+        <v>19</v>
+      </c>
+      <c r="C116" t="s">
+        <v>838</v>
+      </c>
+      <c r="D116" t="s">
+        <v>13</v>
+      </c>
+      <c r="E116" t="b">
+        <v>0</v>
+      </c>
+      <c r="F116" t="s">
+        <v>37</v>
+      </c>
+      <c r="G116">
+        <v>1</v>
+      </c>
+      <c r="H116" t="s">
+        <v>682</v>
+      </c>
+      <c r="I116" t="s">
+        <v>683</v>
+      </c>
+      <c r="J116">
+        <v>0</v>
+      </c>
+      <c r="K116">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="117" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A117" t="s">
+        <v>166</v>
+      </c>
+      <c r="B117" t="s">
+        <v>167</v>
+      </c>
+      <c r="C117" t="s">
+        <v>524</v>
+      </c>
+      <c r="D117" t="s">
+        <v>13</v>
+      </c>
+      <c r="E117" t="b">
+        <v>0</v>
+      </c>
+      <c r="F117" t="s">
+        <v>37</v>
+      </c>
+      <c r="G117">
+        <v>1</v>
+      </c>
+      <c r="H117" t="s">
+        <v>682</v>
+      </c>
+      <c r="I117" t="s">
+        <v>683</v>
+      </c>
+      <c r="J117">
+        <v>0</v>
+      </c>
+      <c r="K117">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="118" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A118" t="s">
+        <v>40</v>
+      </c>
+      <c r="B118" t="s">
+        <v>11</v>
+      </c>
+      <c r="C118" t="s">
+        <v>839</v>
+      </c>
+      <c r="D118" t="s">
+        <v>24</v>
+      </c>
+      <c r="E118" t="b">
+        <v>0</v>
+      </c>
+      <c r="F118" t="s">
+        <v>37</v>
+      </c>
+      <c r="G118">
+        <v>1</v>
+      </c>
+      <c r="H118" t="s">
+        <v>682</v>
+      </c>
+      <c r="I118" t="s">
+        <v>683</v>
+      </c>
+      <c r="J118">
+        <v>0</v>
+      </c>
+      <c r="K118">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="119" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A119" t="s">
+        <v>83</v>
+      </c>
+      <c r="B119" t="s">
+        <v>11</v>
+      </c>
+      <c r="C119" t="s">
+        <v>156</v>
+      </c>
+      <c r="D119" t="s">
+        <v>19</v>
+      </c>
+      <c r="E119" t="b">
+        <v>0</v>
+      </c>
+      <c r="F119" t="s">
+        <v>37</v>
+      </c>
+      <c r="H119" t="s">
+        <v>105</v>
+      </c>
+      <c r="I119" t="s">
+        <v>157</v>
+      </c>
+      <c r="J119">
+        <v>1</v>
+      </c>
+      <c r="K119">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="120" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A120" t="s">
+        <v>40</v>
+      </c>
+      <c r="B120" t="s">
+        <v>11</v>
+      </c>
+      <c r="C120" t="s">
+        <v>158</v>
+      </c>
+      <c r="D120" t="s">
+        <v>24</v>
+      </c>
+      <c r="E120" t="b">
+        <v>0</v>
+      </c>
+      <c r="F120" t="s">
+        <v>37</v>
+      </c>
+      <c r="H120" t="s">
+        <v>105</v>
+      </c>
+      <c r="I120" t="s">
+        <v>157</v>
+      </c>
+      <c r="J120">
+        <v>1</v>
+      </c>
+      <c r="K120">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="121" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A121" t="s">
+        <v>38</v>
+      </c>
+      <c r="B121" t="s">
+        <v>24</v>
+      </c>
+      <c r="C121" t="s">
+        <v>159</v>
+      </c>
+      <c r="D121" t="s">
+        <v>13</v>
+      </c>
+      <c r="E121" t="b">
+        <v>0</v>
+      </c>
+      <c r="F121" t="s">
+        <v>37</v>
+      </c>
+      <c r="H121" t="s">
+        <v>105</v>
+      </c>
+      <c r="I121" t="s">
+        <v>160</v>
+      </c>
+      <c r="J121">
+        <v>2</v>
+      </c>
+      <c r="K121">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="122" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A122" t="s">
+        <v>161</v>
+      </c>
+      <c r="B122" t="s">
+        <v>11</v>
+      </c>
+      <c r="C122" t="s">
+        <v>162</v>
+      </c>
+      <c r="D122" t="s">
+        <v>24</v>
+      </c>
+      <c r="E122" t="b">
+        <v>0</v>
+      </c>
+      <c r="F122" t="s">
+        <v>37</v>
+      </c>
+      <c r="H122" t="s">
+        <v>105</v>
+      </c>
+      <c r="I122" t="s">
+        <v>160</v>
+      </c>
+      <c r="J122">
+        <v>2</v>
+      </c>
+      <c r="K122">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="123" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A123" t="s">
+        <v>40</v>
+      </c>
+      <c r="B123" t="s">
+        <v>19</v>
+      </c>
+      <c r="C123" t="s">
+        <v>163</v>
+      </c>
+      <c r="D123" t="s">
+        <v>24</v>
+      </c>
+      <c r="E123" t="b">
+        <v>0</v>
+      </c>
+      <c r="F123" t="s">
+        <v>37</v>
+      </c>
+      <c r="H123" t="s">
+        <v>105</v>
+      </c>
+      <c r="I123" t="s">
+        <v>160</v>
+      </c>
+      <c r="J123">
+        <v>2</v>
+      </c>
+      <c r="K123">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="124" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A124" t="s">
+        <v>40</v>
+      </c>
+      <c r="B124" t="s">
+        <v>11</v>
+      </c>
+      <c r="C124" t="s">
+        <v>164</v>
+      </c>
+      <c r="D124" t="s">
+        <v>24</v>
+      </c>
+      <c r="E124" t="b">
+        <v>0</v>
+      </c>
+      <c r="F124" t="s">
+        <v>37</v>
+      </c>
+      <c r="H124" t="s">
+        <v>105</v>
+      </c>
+      <c r="I124" t="s">
+        <v>165</v>
+      </c>
+      <c r="J124">
+        <v>3</v>
+      </c>
+      <c r="K124">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="125" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A125" t="s">
+        <v>166</v>
+      </c>
+      <c r="B125" t="s">
+        <v>167</v>
+      </c>
+      <c r="C125" t="s">
+        <v>168</v>
+      </c>
+      <c r="D125" t="s">
+        <v>13</v>
+      </c>
+      <c r="E125" t="b">
+        <v>0</v>
+      </c>
+      <c r="F125" t="s">
+        <v>37</v>
+      </c>
+      <c r="H125" t="s">
+        <v>105</v>
+      </c>
+      <c r="I125" t="s">
+        <v>169</v>
+      </c>
+      <c r="J125">
+        <v>4</v>
+      </c>
+      <c r="K125">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="126" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A126" t="s">
+        <v>38</v>
+      </c>
+      <c r="B126" t="s">
+        <v>24</v>
+      </c>
+      <c r="C126" t="s">
+        <v>170</v>
+      </c>
+      <c r="D126" t="s">
+        <v>13</v>
+      </c>
+      <c r="E126" t="b">
+        <v>0</v>
+      </c>
+      <c r="F126" t="s">
+        <v>37</v>
+      </c>
+      <c r="H126" t="s">
+        <v>105</v>
+      </c>
+      <c r="I126" t="s">
+        <v>169</v>
+      </c>
+      <c r="J126">
+        <v>4</v>
+      </c>
+      <c r="K126">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="127" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A127" t="s">
+        <v>40</v>
+      </c>
+      <c r="B127" t="s">
+        <v>11</v>
+      </c>
+      <c r="C127" t="s">
+        <v>171</v>
+      </c>
+      <c r="D127" t="s">
+        <v>24</v>
+      </c>
+      <c r="E127" t="b">
+        <v>0</v>
+      </c>
+      <c r="F127" t="s">
+        <v>37</v>
+      </c>
+      <c r="H127" t="s">
+        <v>105</v>
+      </c>
+      <c r="I127" t="s">
+        <v>169</v>
+      </c>
+      <c r="J127">
+        <v>4</v>
+      </c>
+      <c r="K127">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="128" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A128" t="s">
+        <v>40</v>
+      </c>
+      <c r="B128" t="s">
+        <v>11</v>
+      </c>
+      <c r="C128" t="s">
+        <v>172</v>
+      </c>
+      <c r="D128" t="s">
+        <v>24</v>
+      </c>
+      <c r="E128" t="b">
+        <v>0</v>
+      </c>
+      <c r="F128" t="s">
+        <v>37</v>
+      </c>
+      <c r="H128" t="s">
+        <v>105</v>
+      </c>
+      <c r="I128" t="s">
+        <v>173</v>
+      </c>
+      <c r="J128">
+        <v>5</v>
+      </c>
+      <c r="K128">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="129" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A129" t="s">
+        <v>174</v>
+      </c>
+      <c r="B129" t="s">
+        <v>19</v>
+      </c>
+      <c r="C129" t="s">
+        <v>175</v>
+      </c>
+      <c r="D129" t="s">
+        <v>11</v>
+      </c>
+      <c r="E129" t="b">
+        <v>0</v>
+      </c>
+      <c r="F129" t="s">
+        <v>44</v>
+      </c>
+      <c r="H129" t="s">
+        <v>105</v>
+      </c>
+      <c r="I129" t="s">
+        <v>176</v>
+      </c>
+      <c r="J129">
+        <v>1</v>
+      </c>
+      <c r="K129">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="130" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A130" t="s">
+        <v>47</v>
+      </c>
+      <c r="B130" t="s">
+        <v>19</v>
+      </c>
+      <c r="C130" t="s">
+        <v>177</v>
+      </c>
+      <c r="D130" t="s">
+        <v>13</v>
+      </c>
+      <c r="E130" t="b">
+        <v>0</v>
+      </c>
+      <c r="F130" t="s">
+        <v>44</v>
+      </c>
+      <c r="H130" t="s">
+        <v>105</v>
+      </c>
+      <c r="I130" t="s">
+        <v>176</v>
+      </c>
+      <c r="J130">
+        <v>1</v>
+      </c>
+      <c r="K130">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="131" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A131" t="s">
+        <v>69</v>
+      </c>
+      <c r="B131" t="s">
+        <v>19</v>
+      </c>
+      <c r="C131" t="s">
+        <v>178</v>
+      </c>
+      <c r="D131" t="s">
+        <v>11</v>
+      </c>
+      <c r="E131" t="b">
+        <v>0</v>
+      </c>
+      <c r="F131" t="s">
+        <v>44</v>
+      </c>
+      <c r="H131" t="s">
+        <v>105</v>
+      </c>
+      <c r="I131" t="s">
+        <v>176</v>
+      </c>
+      <c r="J131">
+        <v>1</v>
+      </c>
+      <c r="K131">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="132" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A132" t="s">
+        <v>59</v>
+      </c>
+      <c r="B132" t="s">
+        <v>11</v>
+      </c>
+      <c r="C132" t="s">
+        <v>182</v>
+      </c>
+      <c r="D132" t="s">
+        <v>13</v>
+      </c>
+      <c r="E132" t="b">
+        <v>0</v>
+      </c>
+      <c r="F132" t="s">
+        <v>44</v>
+      </c>
+      <c r="H132" t="s">
+        <v>105</v>
+      </c>
+      <c r="I132" t="s">
+        <v>176</v>
+      </c>
+      <c r="J132">
+        <v>1</v>
+      </c>
+      <c r="K132">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="133" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A133" t="s">
+        <v>49</v>
+      </c>
+      <c r="B133" t="s">
+        <v>19</v>
+      </c>
+      <c r="C133" t="s">
+        <v>183</v>
+      </c>
+      <c r="D133" t="s">
+        <v>24</v>
+      </c>
+      <c r="E133" t="b">
+        <v>0</v>
+      </c>
+      <c r="F133" t="s">
+        <v>44</v>
+      </c>
+      <c r="H133" t="s">
+        <v>105</v>
+      </c>
+      <c r="I133" t="s">
+        <v>176</v>
+      </c>
+      <c r="J133">
+        <v>1</v>
+      </c>
+      <c r="K133">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="134" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A134" t="s">
+        <v>53</v>
+      </c>
+      <c r="B134" t="s">
+        <v>11</v>
+      </c>
+      <c r="C134" t="s">
+        <v>184</v>
+      </c>
+      <c r="D134" t="s">
+        <v>24</v>
+      </c>
+      <c r="E134" t="b">
+        <v>0</v>
+      </c>
+      <c r="F134" t="s">
+        <v>44</v>
+      </c>
+      <c r="H134" t="s">
+        <v>105</v>
+      </c>
+      <c r="I134" t="s">
+        <v>176</v>
+      </c>
+      <c r="J134">
+        <v>1</v>
+      </c>
+      <c r="K134">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="135" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A135" t="s">
+        <v>67</v>
+      </c>
+      <c r="B135" t="s">
+        <v>19</v>
+      </c>
+      <c r="C135" t="s">
+        <v>189</v>
+      </c>
+      <c r="D135" t="s">
+        <v>13</v>
+      </c>
+      <c r="E135" t="b">
+        <v>0</v>
+      </c>
+      <c r="F135" t="s">
+        <v>44</v>
+      </c>
+      <c r="H135" t="s">
+        <v>105</v>
+      </c>
+      <c r="I135" t="s">
+        <v>176</v>
+      </c>
+      <c r="J135">
+        <v>1</v>
+      </c>
+      <c r="K135">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="136" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A136" t="s">
+        <v>42</v>
+      </c>
+      <c r="B136" t="s">
+        <v>11</v>
+      </c>
+      <c r="C136" t="s">
+        <v>190</v>
+      </c>
+      <c r="D136" t="s">
+        <v>13</v>
+      </c>
+      <c r="E136" t="b">
+        <v>0</v>
+      </c>
+      <c r="F136" t="s">
+        <v>44</v>
+      </c>
+      <c r="H136" t="s">
+        <v>105</v>
+      </c>
+      <c r="I136" t="s">
+        <v>176</v>
+      </c>
+      <c r="J136">
+        <v>1</v>
+      </c>
+      <c r="K136">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="137" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A137" t="s">
+        <v>51</v>
+      </c>
+      <c r="B137" t="s">
+        <v>11</v>
+      </c>
+      <c r="C137" t="s">
+        <v>191</v>
+      </c>
+      <c r="D137" t="s">
+        <v>13</v>
+      </c>
+      <c r="E137" t="b">
+        <v>0</v>
+      </c>
+      <c r="F137" t="s">
+        <v>44</v>
+      </c>
+      <c r="H137" t="s">
+        <v>105</v>
+      </c>
+      <c r="I137" t="s">
+        <v>176</v>
+      </c>
+      <c r="J137">
+        <v>1</v>
+      </c>
+      <c r="K137">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="138" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A138" t="s">
+        <v>53</v>
+      </c>
+      <c r="B138" t="s">
+        <v>11</v>
+      </c>
+      <c r="C138" t="s">
+        <v>195</v>
+      </c>
+      <c r="D138" t="s">
+        <v>24</v>
+      </c>
+      <c r="E138" t="b">
+        <v>0</v>
+      </c>
+      <c r="F138" t="s">
+        <v>44</v>
+      </c>
+      <c r="H138" t="s">
+        <v>105</v>
+      </c>
+      <c r="I138" t="s">
+        <v>196</v>
+      </c>
+      <c r="J138">
+        <v>2</v>
+      </c>
+      <c r="K138">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="139" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A139" t="s">
+        <v>65</v>
+      </c>
+      <c r="B139" t="s">
+        <v>11</v>
+      </c>
+      <c r="C139" t="s">
+        <v>197</v>
+      </c>
+      <c r="D139" t="s">
+        <v>13</v>
+      </c>
+      <c r="E139" t="b">
+        <v>0</v>
+      </c>
+      <c r="F139" t="s">
+        <v>44</v>
+      </c>
+      <c r="H139" t="s">
+        <v>105</v>
+      </c>
+      <c r="I139" t="s">
+        <v>196</v>
+      </c>
+      <c r="J139">
+        <v>2</v>
+      </c>
+      <c r="K139">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="140" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A140" t="s">
+        <v>47</v>
+      </c>
+      <c r="B140" t="s">
+        <v>19</v>
+      </c>
+      <c r="C140" t="s">
+        <v>198</v>
+      </c>
+      <c r="D140" t="s">
+        <v>13</v>
+      </c>
+      <c r="E140" t="b">
+        <v>0</v>
+      </c>
+      <c r="F140" t="s">
+        <v>44</v>
+      </c>
+      <c r="H140" t="s">
+        <v>105</v>
+      </c>
+      <c r="I140" t="s">
+        <v>196</v>
+      </c>
+      <c r="J140">
+        <v>2</v>
+      </c>
+      <c r="K140">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="141" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A141" t="s">
+        <v>55</v>
+      </c>
+      <c r="B141" t="s">
+        <v>24</v>
+      </c>
+      <c r="C141" t="s">
+        <v>202</v>
+      </c>
+      <c r="D141" t="s">
+        <v>19</v>
+      </c>
+      <c r="E141" t="b">
+        <v>0</v>
+      </c>
+      <c r="F141" t="s">
+        <v>44</v>
+      </c>
+      <c r="H141" t="s">
+        <v>105</v>
+      </c>
+      <c r="I141" t="s">
+        <v>196</v>
+      </c>
+      <c r="J141">
+        <v>2</v>
+      </c>
+      <c r="K141">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="142" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A142" t="s">
+        <v>57</v>
+      </c>
+      <c r="B142" t="s">
+        <v>11</v>
+      </c>
+      <c r="C142" t="s">
+        <v>203</v>
+      </c>
+      <c r="D142" t="s">
+        <v>13</v>
+      </c>
+      <c r="E142" t="b">
+        <v>0</v>
+      </c>
+      <c r="F142" t="s">
+        <v>44</v>
+      </c>
+      <c r="H142" t="s">
+        <v>105</v>
+      </c>
+      <c r="I142" t="s">
+        <v>196</v>
+      </c>
+      <c r="J142">
+        <v>2</v>
+      </c>
+      <c r="K142">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="143" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A143" t="s">
+        <v>59</v>
+      </c>
+      <c r="B143" t="s">
+        <v>11</v>
+      </c>
+      <c r="C143" t="s">
+        <v>204</v>
+      </c>
+      <c r="D143" t="s">
+        <v>13</v>
+      </c>
+      <c r="E143" t="b">
+        <v>0</v>
+      </c>
+      <c r="F143" t="s">
+        <v>44</v>
+      </c>
+      <c r="H143" t="s">
+        <v>105</v>
+      </c>
+      <c r="I143" t="s">
+        <v>196</v>
+      </c>
+      <c r="J143">
+        <v>2</v>
+      </c>
+      <c r="K143">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="144" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A144" t="s">
+        <v>45</v>
+      </c>
+      <c r="B144" t="s">
+        <v>19</v>
+      </c>
+      <c r="C144" t="s">
+        <v>208</v>
+      </c>
+      <c r="D144" t="s">
+        <v>13</v>
+      </c>
+      <c r="E144" t="b">
+        <v>0</v>
+      </c>
+      <c r="F144" t="s">
+        <v>44</v>
+      </c>
+      <c r="H144" t="s">
+        <v>105</v>
+      </c>
+      <c r="I144" t="s">
+        <v>196</v>
+      </c>
+      <c r="J144">
+        <v>2</v>
+      </c>
+      <c r="K144">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="145" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A145" t="s">
+        <v>67</v>
+      </c>
+      <c r="B145" t="s">
+        <v>19</v>
+      </c>
+      <c r="C145" t="s">
+        <v>209</v>
+      </c>
+      <c r="D145" t="s">
+        <v>13</v>
+      </c>
+      <c r="E145" t="b">
+        <v>0</v>
+      </c>
+      <c r="F145" t="s">
+        <v>44</v>
+      </c>
+      <c r="H145" t="s">
+        <v>105</v>
+      </c>
+      <c r="I145" t="s">
+        <v>196</v>
+      </c>
+      <c r="J145">
+        <v>2</v>
+      </c>
+      <c r="K145">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="146" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A146" t="s">
+        <v>51</v>
+      </c>
+      <c r="B146" t="s">
+        <v>11</v>
+      </c>
+      <c r="C146" t="s">
+        <v>210</v>
+      </c>
+      <c r="D146" t="s">
+        <v>13</v>
+      </c>
+      <c r="E146" t="b">
+        <v>0</v>
+      </c>
+      <c r="F146" t="s">
+        <v>44</v>
+      </c>
+      <c r="H146" t="s">
+        <v>105</v>
+      </c>
+      <c r="I146" t="s">
+        <v>196</v>
+      </c>
+      <c r="J146">
+        <v>2</v>
+      </c>
+      <c r="K146">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="147" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A147" t="s">
+        <v>49</v>
+      </c>
+      <c r="B147" t="s">
+        <v>19</v>
+      </c>
+      <c r="C147" t="s">
+        <v>216</v>
+      </c>
+      <c r="D147" t="s">
+        <v>24</v>
+      </c>
+      <c r="E147" t="b">
+        <v>0</v>
+      </c>
+      <c r="F147" t="s">
+        <v>44</v>
+      </c>
+      <c r="H147" t="s">
+        <v>105</v>
+      </c>
+      <c r="I147" t="s">
+        <v>212</v>
+      </c>
+      <c r="J147">
+        <v>3</v>
+      </c>
+      <c r="K147">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="148" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A148" t="s">
+        <v>45</v>
+      </c>
+      <c r="B148" t="s">
+        <v>19</v>
+      </c>
+      <c r="C148" t="s">
+        <v>217</v>
+      </c>
+      <c r="D148" t="s">
+        <v>13</v>
+      </c>
+      <c r="E148" t="b">
+        <v>0</v>
+      </c>
+      <c r="F148" t="s">
+        <v>44</v>
+      </c>
+      <c r="H148" t="s">
+        <v>105</v>
+      </c>
+      <c r="I148" t="s">
+        <v>212</v>
+      </c>
+      <c r="J148">
+        <v>3</v>
+      </c>
+      <c r="K148">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="149" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A149" t="s">
+        <v>42</v>
+      </c>
+      <c r="B149" t="s">
+        <v>24</v>
+      </c>
+      <c r="C149" t="s">
+        <v>218</v>
+      </c>
+      <c r="D149" t="s">
+        <v>13</v>
+      </c>
+      <c r="E149" t="b">
+        <v>0</v>
+      </c>
+      <c r="F149" t="s">
+        <v>44</v>
+      </c>
+      <c r="H149" t="s">
+        <v>105</v>
+      </c>
+      <c r="I149" t="s">
+        <v>212</v>
+      </c>
+      <c r="J149">
+        <v>3</v>
+      </c>
+      <c r="K149">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="150" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A150" t="s">
+        <v>59</v>
+      </c>
+      <c r="B150" t="s">
+        <v>11</v>
+      </c>
+      <c r="C150" t="s">
+        <v>223</v>
+      </c>
+      <c r="D150" t="s">
+        <v>13</v>
+      </c>
+      <c r="E150" t="b">
+        <v>0</v>
+      </c>
+      <c r="F150" t="s">
+        <v>44</v>
+      </c>
+      <c r="H150" t="s">
+        <v>105</v>
+      </c>
+      <c r="I150" t="s">
+        <v>212</v>
+      </c>
+      <c r="J150">
+        <v>3</v>
+      </c>
+      <c r="K150">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="151" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A151" t="s">
+        <v>51</v>
+      </c>
+      <c r="B151" t="s">
+        <v>11</v>
+      </c>
+      <c r="C151" t="s">
+        <v>224</v>
+      </c>
+      <c r="D151" t="s">
+        <v>13</v>
+      </c>
+      <c r="E151" t="b">
+        <v>0</v>
+      </c>
+      <c r="F151" t="s">
+        <v>44</v>
+      </c>
+      <c r="H151" t="s">
+        <v>105</v>
+      </c>
+      <c r="I151" t="s">
+        <v>212</v>
+      </c>
+      <c r="J151">
+        <v>3</v>
+      </c>
+      <c r="K151">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="152" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A152" t="s">
+        <v>63</v>
+      </c>
+      <c r="B152" t="s">
+        <v>11</v>
+      </c>
+      <c r="C152" t="s">
+        <v>225</v>
+      </c>
+      <c r="D152" t="s">
+        <v>13</v>
+      </c>
+      <c r="E152" t="b">
+        <v>0</v>
+      </c>
+      <c r="F152" t="s">
+        <v>44</v>
+      </c>
+      <c r="H152" t="s">
+        <v>105</v>
+      </c>
+      <c r="I152" t="s">
+        <v>212</v>
+      </c>
+      <c r="J152">
+        <v>3</v>
+      </c>
+      <c r="K152">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="153" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A153" t="s">
+        <v>53</v>
+      </c>
+      <c r="B153" t="s">
+        <v>11</v>
+      </c>
+      <c r="C153" t="s">
+        <v>226</v>
+      </c>
+      <c r="D153" t="s">
+        <v>24</v>
+      </c>
+      <c r="E153" t="b">
+        <v>0</v>
+      </c>
+      <c r="F153" t="s">
+        <v>44</v>
+      </c>
+      <c r="H153" t="s">
+        <v>105</v>
+      </c>
+      <c r="I153" t="s">
+        <v>212</v>
+      </c>
+      <c r="J153">
+        <v>3</v>
+      </c>
+      <c r="K153">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="154" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A154" t="s">
+        <v>65</v>
+      </c>
+      <c r="B154" t="s">
+        <v>11</v>
+      </c>
+      <c r="C154" t="s">
+        <v>227</v>
+      </c>
+      <c r="D154" t="s">
+        <v>13</v>
+      </c>
+      <c r="E154" t="b">
+        <v>0</v>
+      </c>
+      <c r="F154" t="s">
+        <v>44</v>
+      </c>
+      <c r="H154" t="s">
+        <v>105</v>
+      </c>
+      <c r="I154" t="s">
+        <v>212</v>
+      </c>
+      <c r="J154">
+        <v>3</v>
+      </c>
+      <c r="K154">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="155" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A155" t="s">
+        <v>61</v>
+      </c>
+      <c r="B155" t="s">
+        <v>19</v>
+      </c>
+      <c r="C155" t="s">
+        <v>228</v>
+      </c>
+      <c r="D155" t="s">
+        <v>24</v>
+      </c>
+      <c r="E155" t="b">
+        <v>0</v>
+      </c>
+      <c r="F155" t="s">
+        <v>44</v>
+      </c>
+      <c r="H155" t="s">
+        <v>105</v>
+      </c>
+      <c r="I155" t="s">
+        <v>212</v>
+      </c>
+      <c r="J155">
+        <v>3</v>
+      </c>
+      <c r="K155">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="156" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A156" t="s">
+        <v>69</v>
+      </c>
+      <c r="B156" t="s">
+        <v>24</v>
+      </c>
+      <c r="C156" t="s">
+        <v>229</v>
+      </c>
+      <c r="D156" t="s">
+        <v>11</v>
+      </c>
+      <c r="E156" t="b">
+        <v>0</v>
+      </c>
+      <c r="F156" t="s">
+        <v>44</v>
+      </c>
+      <c r="H156" t="s">
+        <v>105</v>
+      </c>
+      <c r="I156" t="s">
+        <v>212</v>
+      </c>
+      <c r="J156">
+        <v>3</v>
+      </c>
+      <c r="K156">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="157" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A157" t="s">
+        <v>47</v>
+      </c>
+      <c r="B157" t="s">
+        <v>19</v>
+      </c>
+      <c r="C157" t="s">
+        <v>230</v>
+      </c>
+      <c r="D157" t="s">
+        <v>13</v>
+      </c>
+      <c r="E157" t="b">
+        <v>0</v>
+      </c>
+      <c r="F157" t="s">
+        <v>44</v>
+      </c>
+      <c r="H157" t="s">
+        <v>105</v>
+      </c>
+      <c r="I157" t="s">
+        <v>231</v>
+      </c>
+      <c r="J157">
+        <v>4</v>
+      </c>
+      <c r="K157">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="158" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A158" t="s">
+        <v>57</v>
+      </c>
+      <c r="B158" t="s">
+        <v>11</v>
+      </c>
+      <c r="C158" t="s">
+        <v>232</v>
+      </c>
+      <c r="D158" t="s">
+        <v>13</v>
+      </c>
+      <c r="E158" t="b">
+        <v>0</v>
+      </c>
+      <c r="F158" t="s">
+        <v>44</v>
+      </c>
+      <c r="H158" t="s">
+        <v>105</v>
+      </c>
+      <c r="I158" t="s">
+        <v>231</v>
+      </c>
+      <c r="J158">
+        <v>4</v>
+      </c>
+      <c r="K158">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="159" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A159" t="s">
+        <v>97</v>
+      </c>
+      <c r="B159" t="s">
+        <v>19</v>
+      </c>
+      <c r="C159" t="s">
+        <v>233</v>
+      </c>
+      <c r="D159" t="s">
+        <v>24</v>
+      </c>
+      <c r="E159" t="b">
+        <v>0</v>
+      </c>
+      <c r="F159" t="s">
+        <v>44</v>
+      </c>
+      <c r="H159" t="s">
+        <v>105</v>
+      </c>
+      <c r="I159" t="s">
+        <v>231</v>
+      </c>
+      <c r="J159">
+        <v>4</v>
+      </c>
+      <c r="K159">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="160" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A160" t="s">
+        <v>214</v>
+      </c>
+      <c r="B160" t="s">
+        <v>19</v>
+      </c>
+      <c r="C160" t="s">
+        <v>237</v>
+      </c>
+      <c r="D160" t="s">
+        <v>11</v>
+      </c>
+      <c r="E160" t="b">
+        <v>0</v>
+      </c>
+      <c r="F160" t="s">
+        <v>44</v>
+      </c>
+      <c r="H160" t="s">
+        <v>105</v>
+      </c>
+      <c r="I160" t="s">
+        <v>231</v>
+      </c>
+      <c r="J160">
+        <v>4</v>
+      </c>
+      <c r="K160">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="161" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A161" t="s">
+        <v>65</v>
+      </c>
+      <c r="B161" t="s">
+        <v>11</v>
+      </c>
+      <c r="C161" t="s">
+        <v>238</v>
+      </c>
+      <c r="D161" t="s">
+        <v>13</v>
+      </c>
+      <c r="E161" t="b">
+        <v>0</v>
+      </c>
+      <c r="F161" t="s">
+        <v>44</v>
+      </c>
+      <c r="H161" t="s">
+        <v>105</v>
+      </c>
+      <c r="I161" t="s">
+        <v>231</v>
+      </c>
+      <c r="J161">
+        <v>4</v>
+      </c>
+      <c r="K161">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="162" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A162" t="s">
+        <v>55</v>
+      </c>
+      <c r="B162" t="s">
+        <v>24</v>
+      </c>
+      <c r="C162" t="s">
+        <v>239</v>
+      </c>
+      <c r="D162" t="s">
+        <v>19</v>
+      </c>
+      <c r="E162" t="b">
+        <v>0</v>
+      </c>
+      <c r="F162" t="s">
+        <v>44</v>
+      </c>
+      <c r="H162" t="s">
+        <v>105</v>
+      </c>
+      <c r="I162" t="s">
+        <v>231</v>
+      </c>
+      <c r="J162">
+        <v>4</v>
+      </c>
+      <c r="K162">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="163" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A163" t="s">
+        <v>51</v>
+      </c>
+      <c r="B163" t="s">
+        <v>11</v>
+      </c>
+      <c r="C163" t="s">
+        <v>243</v>
+      </c>
+      <c r="D163" t="s">
+        <v>13</v>
+      </c>
+      <c r="E163" t="b">
+        <v>0</v>
+      </c>
+      <c r="F163" t="s">
+        <v>44</v>
+      </c>
+      <c r="H163" t="s">
+        <v>105</v>
+      </c>
+      <c r="I163" t="s">
+        <v>231</v>
+      </c>
+      <c r="J163">
+        <v>4</v>
+      </c>
+      <c r="K163">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="164" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A164" t="s">
+        <v>92</v>
+      </c>
+      <c r="B164" t="s">
+        <v>19</v>
+      </c>
+      <c r="C164" t="s">
+        <v>244</v>
+      </c>
+      <c r="D164" t="s">
+        <v>13</v>
+      </c>
+      <c r="E164" t="b">
+        <v>0</v>
+      </c>
+      <c r="F164" t="s">
+        <v>44</v>
+      </c>
+      <c r="H164" t="s">
+        <v>105</v>
+      </c>
+      <c r="I164" t="s">
+        <v>231</v>
+      </c>
+      <c r="J164">
+        <v>4</v>
+      </c>
+      <c r="K164">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="165" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A165" t="s">
+        <v>42</v>
+      </c>
+      <c r="B165" t="s">
+        <v>24</v>
+      </c>
+      <c r="C165" t="s">
+        <v>245</v>
+      </c>
+      <c r="D165" t="s">
+        <v>13</v>
+      </c>
+      <c r="E165" t="b">
+        <v>0</v>
+      </c>
+      <c r="F165" t="s">
+        <v>44</v>
+      </c>
+      <c r="H165" t="s">
+        <v>105</v>
+      </c>
+      <c r="I165" t="s">
+        <v>231</v>
+      </c>
+      <c r="J165">
+        <v>4</v>
+      </c>
+      <c r="K165">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="166" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A166" t="s">
+        <v>67</v>
+      </c>
+      <c r="B166" t="s">
+        <v>19</v>
+      </c>
+      <c r="C166" t="s">
+        <v>246</v>
+      </c>
+      <c r="D166" t="s">
+        <v>13</v>
+      </c>
+      <c r="E166" t="b">
+        <v>0</v>
+      </c>
+      <c r="F166" t="s">
+        <v>44</v>
+      </c>
+      <c r="H166" t="s">
+        <v>105</v>
+      </c>
+      <c r="I166" t="s">
+        <v>231</v>
+      </c>
+      <c r="J166">
+        <v>4</v>
+      </c>
+      <c r="K166">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="167" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A167" t="s">
+        <v>90</v>
+      </c>
+      <c r="B167" t="s">
+        <v>24</v>
+      </c>
+      <c r="C167" t="s">
+        <v>247</v>
+      </c>
+      <c r="D167" t="s">
+        <v>11</v>
+      </c>
+      <c r="E167" t="b">
+        <v>0</v>
+      </c>
+      <c r="F167" t="s">
+        <v>44</v>
+      </c>
+      <c r="H167" t="s">
+        <v>105</v>
+      </c>
+      <c r="I167" t="s">
+        <v>231</v>
+      </c>
+      <c r="J167">
+        <v>4</v>
+      </c>
+      <c r="K167">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="168" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A168" t="s">
+        <v>42</v>
+      </c>
+      <c r="B168" t="s">
+        <v>24</v>
+      </c>
+      <c r="C168" t="s">
+        <v>248</v>
+      </c>
+      <c r="D168" t="s">
+        <v>13</v>
+      </c>
+      <c r="E168" t="b">
+        <v>0</v>
+      </c>
+      <c r="F168" t="s">
+        <v>44</v>
+      </c>
+      <c r="H168" t="s">
+        <v>105</v>
+      </c>
+      <c r="I168" t="s">
+        <v>249</v>
+      </c>
+      <c r="J168">
+        <v>5</v>
+      </c>
+      <c r="K168">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="169" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A169" t="s">
+        <v>45</v>
+      </c>
+      <c r="B169" t="s">
+        <v>19</v>
+      </c>
+      <c r="C169" t="s">
+        <v>250</v>
+      </c>
+      <c r="D169" t="s">
+        <v>13</v>
+      </c>
+      <c r="E169" t="b">
+        <v>0</v>
+      </c>
+      <c r="F169" t="s">
+        <v>44</v>
+      </c>
+      <c r="H169" t="s">
+        <v>105</v>
+      </c>
+      <c r="I169" t="s">
+        <v>249</v>
+      </c>
+      <c r="J169">
+        <v>5</v>
+      </c>
+      <c r="K169">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="170" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A170" t="s">
+        <v>47</v>
+      </c>
+      <c r="B170" t="s">
+        <v>19</v>
+      </c>
+      <c r="C170" t="s">
+        <v>251</v>
+      </c>
+      <c r="D170" t="s">
+        <v>13</v>
+      </c>
+      <c r="E170" t="b">
+        <v>0</v>
+      </c>
+      <c r="F170" t="s">
+        <v>44</v>
+      </c>
+      <c r="H170" t="s">
+        <v>105</v>
+      </c>
+      <c r="I170" t="s">
+        <v>249</v>
+      </c>
+      <c r="J170">
+        <v>5</v>
+      </c>
+      <c r="K170">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="171" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A171" t="s">
+        <v>49</v>
+      </c>
+      <c r="B171" t="s">
+        <v>19</v>
+      </c>
+      <c r="C171" t="s">
+        <v>252</v>
+      </c>
+      <c r="D171" t="s">
+        <v>24</v>
+      </c>
+      <c r="E171" t="b">
+        <v>0</v>
+      </c>
+      <c r="F171" t="s">
+        <v>44</v>
+      </c>
+      <c r="H171" t="s">
+        <v>105</v>
+      </c>
+      <c r="I171" t="s">
+        <v>249</v>
+      </c>
+      <c r="J171">
+        <v>5</v>
+      </c>
+      <c r="K171">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="172" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A172" t="s">
+        <v>51</v>
+      </c>
+      <c r="B172" t="s">
+        <v>11</v>
+      </c>
+      <c r="C172" t="s">
+        <v>253</v>
+      </c>
+      <c r="D172" t="s">
+        <v>13</v>
+      </c>
+      <c r="E172" t="b">
+        <v>0</v>
+      </c>
+      <c r="F172" t="s">
+        <v>44</v>
+      </c>
+      <c r="H172" t="s">
+        <v>105</v>
+      </c>
+      <c r="I172" t="s">
+        <v>249</v>
+      </c>
+      <c r="J172">
+        <v>5</v>
+      </c>
+      <c r="K172">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="173" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A173" t="s">
+        <v>61</v>
+      </c>
+      <c r="B173" t="s">
+        <v>19</v>
+      </c>
+      <c r="C173" t="s">
+        <v>258</v>
+      </c>
+      <c r="D173" t="s">
+        <v>24</v>
+      </c>
+      <c r="E173" t="b">
+        <v>0</v>
+      </c>
+      <c r="F173" t="s">
+        <v>44</v>
+      </c>
+      <c r="H173" t="s">
+        <v>105</v>
+      </c>
+      <c r="I173" t="s">
+        <v>249</v>
+      </c>
+      <c r="J173">
+        <v>5</v>
+      </c>
+      <c r="K173">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="174" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A174" t="s">
+        <v>92</v>
+      </c>
+      <c r="B174" t="s">
+        <v>19</v>
+      </c>
+      <c r="C174" t="s">
+        <v>259</v>
+      </c>
+      <c r="D174" t="s">
+        <v>13</v>
+      </c>
+      <c r="E174" t="b">
+        <v>0</v>
+      </c>
+      <c r="F174" t="s">
+        <v>44</v>
+      </c>
+      <c r="H174" t="s">
+        <v>105</v>
+      </c>
+      <c r="I174" t="s">
+        <v>249</v>
+      </c>
+      <c r="J174">
+        <v>5</v>
+      </c>
+      <c r="K174">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="175" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A175" t="s">
+        <v>65</v>
+      </c>
+      <c r="B175" t="s">
+        <v>11</v>
+      </c>
+      <c r="C175" t="s">
+        <v>260</v>
+      </c>
+      <c r="D175" t="s">
+        <v>13</v>
+      </c>
+      <c r="E175" t="b">
+        <v>0</v>
+      </c>
+      <c r="F175" t="s">
+        <v>44</v>
+      </c>
+      <c r="H175" t="s">
+        <v>105</v>
+      </c>
+      <c r="I175" t="s">
+        <v>249</v>
+      </c>
+      <c r="J175">
+        <v>5</v>
+      </c>
+      <c r="K175">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="176" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A176" t="s">
+        <v>67</v>
+      </c>
+      <c r="B176" t="s">
+        <v>19</v>
+      </c>
+      <c r="C176" t="s">
+        <v>261</v>
+      </c>
+      <c r="D176" t="s">
+        <v>13</v>
+      </c>
+      <c r="E176" t="b">
+        <v>0</v>
+      </c>
+      <c r="F176" t="s">
+        <v>44</v>
+      </c>
+      <c r="H176" t="s">
+        <v>105</v>
+      </c>
+      <c r="I176" t="s">
+        <v>249</v>
+      </c>
+      <c r="J176">
+        <v>5</v>
+      </c>
+      <c r="K176">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="177" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A177" t="s">
+        <v>63</v>
+      </c>
+      <c r="B177" t="s">
+        <v>11</v>
+      </c>
+      <c r="C177" t="s">
+        <v>262</v>
+      </c>
+      <c r="D177" t="s">
+        <v>13</v>
+      </c>
+      <c r="E177" t="b">
+        <v>0</v>
+      </c>
+      <c r="F177" t="s">
+        <v>44</v>
+      </c>
+      <c r="H177" t="s">
+        <v>105</v>
+      </c>
+      <c r="I177" t="s">
+        <v>249</v>
+      </c>
+      <c r="J177">
+        <v>5</v>
+      </c>
+      <c r="K177">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="178" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A178" t="s">
+        <v>25</v>
+      </c>
+      <c r="B178" t="s">
+        <v>13</v>
+      </c>
+      <c r="C178" t="s">
+        <v>108</v>
+      </c>
+      <c r="D178" t="s">
+        <v>24</v>
+      </c>
+      <c r="E178" t="b">
+        <v>0</v>
+      </c>
+      <c r="F178" t="s">
+        <v>14</v>
+      </c>
+      <c r="H178" t="s">
+        <v>105</v>
+      </c>
+      <c r="I178" t="s">
+        <v>106</v>
+      </c>
+      <c r="J178">
+        <v>1</v>
+      </c>
+      <c r="K178">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="179" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A179" t="s">
+        <v>77</v>
+      </c>
+      <c r="B179" t="s">
+        <v>13</v>
+      </c>
+      <c r="C179" t="s">
+        <v>109</v>
+      </c>
+      <c r="D179" t="s">
+        <v>19</v>
+      </c>
+      <c r="E179" t="b">
+        <v>0</v>
+      </c>
+      <c r="F179" t="s">
+        <v>14</v>
+      </c>
+      <c r="H179" t="s">
+        <v>105</v>
+      </c>
+      <c r="I179" t="s">
+        <v>106</v>
+      </c>
+      <c r="J179">
+        <v>1</v>
+      </c>
+      <c r="K179">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="180" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A180" t="s">
+        <v>110</v>
+      </c>
+      <c r="B180" t="s">
+        <v>13</v>
+      </c>
+      <c r="C180" t="s">
+        <v>111</v>
+      </c>
+      <c r="D180" t="s">
+        <v>11</v>
+      </c>
+      <c r="E180" t="b">
+        <v>0</v>
+      </c>
+      <c r="F180" t="s">
+        <v>14</v>
+      </c>
+      <c r="H180" t="s">
+        <v>105</v>
+      </c>
+      <c r="I180" t="s">
+        <v>106</v>
+      </c>
+      <c r="J180">
+        <v>1</v>
+      </c>
+      <c r="K180">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="181" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A181" t="s">
+        <v>27</v>
+      </c>
+      <c r="B181" t="s">
+        <v>19</v>
+      </c>
+      <c r="C181" t="s">
+        <v>112</v>
+      </c>
+      <c r="D181" t="s">
+        <v>11</v>
+      </c>
+      <c r="E181" t="b">
+        <v>0</v>
+      </c>
+      <c r="F181" t="s">
+        <v>14</v>
+      </c>
+      <c r="H181" t="s">
+        <v>105</v>
+      </c>
+      <c r="I181" t="s">
+        <v>106</v>
+      </c>
+      <c r="J181">
+        <v>1</v>
+      </c>
+      <c r="K181">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="182" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A182" t="s">
+        <v>113</v>
+      </c>
+      <c r="B182" t="s">
+        <v>24</v>
+      </c>
+      <c r="C182" t="s">
+        <v>114</v>
+      </c>
+      <c r="D182" t="s">
+        <v>11</v>
+      </c>
+      <c r="E182" t="b">
+        <v>0</v>
+      </c>
+      <c r="F182" t="s">
+        <v>14</v>
+      </c>
+      <c r="H182" t="s">
+        <v>105</v>
+      </c>
+      <c r="I182" t="s">
+        <v>106</v>
+      </c>
+      <c r="J182">
+        <v>1</v>
+      </c>
+      <c r="K182">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="183" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A183" t="s">
+        <v>29</v>
+      </c>
+      <c r="B183" t="s">
+        <v>13</v>
+      </c>
+      <c r="C183" t="s">
+        <v>115</v>
+      </c>
+      <c r="D183" t="s">
+        <v>11</v>
+      </c>
+      <c r="E183" t="b">
+        <v>0</v>
+      </c>
+      <c r="F183" t="s">
+        <v>14</v>
+      </c>
+      <c r="H183" t="s">
+        <v>105</v>
+      </c>
+      <c r="I183" t="s">
+        <v>106</v>
+      </c>
+      <c r="J183">
+        <v>1</v>
+      </c>
+      <c r="K183">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="184" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A184" t="s">
+        <v>10</v>
+      </c>
+      <c r="B184" t="s">
+        <v>11</v>
+      </c>
+      <c r="C184" t="s">
+        <v>116</v>
+      </c>
+      <c r="D184" t="s">
+        <v>13</v>
+      </c>
+      <c r="E184" t="b">
+        <v>0</v>
+      </c>
+      <c r="F184" t="s">
+        <v>14</v>
+      </c>
+      <c r="H184" t="s">
+        <v>105</v>
+      </c>
+      <c r="I184" t="s">
+        <v>106</v>
+      </c>
+      <c r="J184">
+        <v>1</v>
+      </c>
+      <c r="K184">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="185" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A185" t="s">
+        <v>31</v>
+      </c>
+      <c r="B185" t="s">
+        <v>24</v>
+      </c>
+      <c r="C185" t="s">
+        <v>117</v>
+      </c>
+      <c r="D185" t="s">
+        <v>19</v>
+      </c>
+      <c r="E185" t="b">
+        <v>0</v>
+      </c>
+      <c r="F185" t="s">
+        <v>14</v>
+      </c>
+      <c r="H185" t="s">
+        <v>105</v>
+      </c>
+      <c r="I185" t="s">
+        <v>106</v>
+      </c>
+      <c r="J185">
+        <v>1</v>
+      </c>
+      <c r="K185">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="186" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A186" t="s">
+        <v>33</v>
+      </c>
+      <c r="B186" t="s">
+        <v>11</v>
+      </c>
+      <c r="C186" t="s">
+        <v>118</v>
+      </c>
+      <c r="D186" t="s">
+        <v>13</v>
+      </c>
+      <c r="E186" t="b">
+        <v>0</v>
+      </c>
+      <c r="F186" t="s">
+        <v>14</v>
+      </c>
+      <c r="H186" t="s">
+        <v>105</v>
+      </c>
+      <c r="I186" t="s">
+        <v>106</v>
+      </c>
+      <c r="J186">
+        <v>1</v>
+      </c>
+      <c r="K186">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="187" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A187" t="s">
+        <v>113</v>
+      </c>
+      <c r="B187" t="s">
+        <v>24</v>
+      </c>
+      <c r="C187" t="s">
+        <v>119</v>
+      </c>
+      <c r="D187" t="s">
+        <v>11</v>
+      </c>
+      <c r="E187" t="b">
+        <v>0</v>
+      </c>
+      <c r="F187" t="s">
+        <v>14</v>
+      </c>
+      <c r="H187" t="s">
+        <v>105</v>
+      </c>
+      <c r="I187" t="s">
+        <v>120</v>
+      </c>
+      <c r="J187">
+        <v>2</v>
+      </c>
+      <c r="K187">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="188" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A188" t="s">
+        <v>27</v>
+      </c>
+      <c r="B188" t="s">
+        <v>19</v>
+      </c>
+      <c r="C188" t="s">
+        <v>121</v>
+      </c>
+      <c r="D188" t="s">
+        <v>11</v>
+      </c>
+      <c r="E188" t="b">
+        <v>0</v>
+      </c>
+      <c r="F188" t="s">
+        <v>14</v>
+      </c>
+      <c r="H188" t="s">
+        <v>105</v>
+      </c>
+      <c r="I188" t="s">
+        <v>120</v>
+      </c>
+      <c r="J188">
+        <v>2</v>
+      </c>
+      <c r="K188">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="189" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A189" t="s">
+        <v>33</v>
+      </c>
+      <c r="B189" t="s">
+        <v>11</v>
+      </c>
+      <c r="C189" t="s">
+        <v>122</v>
+      </c>
+      <c r="D189" t="s">
+        <v>13</v>
+      </c>
+      <c r="E189" t="b">
+        <v>0</v>
+      </c>
+      <c r="F189" t="s">
+        <v>14</v>
+      </c>
+      <c r="H189" t="s">
+        <v>105</v>
+      </c>
+      <c r="I189" t="s">
+        <v>120</v>
+      </c>
+      <c r="J189">
+        <v>2</v>
+      </c>
+      <c r="K189">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="190" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A190" t="s">
+        <v>17</v>
+      </c>
+      <c r="B190" t="s">
+        <v>11</v>
+      </c>
+      <c r="C190" t="s">
+        <v>123</v>
+      </c>
+      <c r="D190" t="s">
+        <v>19</v>
+      </c>
+      <c r="E190" t="b">
+        <v>0</v>
+      </c>
+      <c r="F190" t="s">
+        <v>14</v>
+      </c>
+      <c r="H190" t="s">
+        <v>105</v>
+      </c>
+      <c r="I190" t="s">
+        <v>120</v>
+      </c>
+      <c r="J190">
+        <v>2</v>
+      </c>
+      <c r="K190">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="191" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A191" t="s">
+        <v>25</v>
+      </c>
+      <c r="B191" t="s">
+        <v>13</v>
+      </c>
+      <c r="C191" t="s">
+        <v>124</v>
+      </c>
+      <c r="D191" t="s">
+        <v>24</v>
+      </c>
+      <c r="E191" t="b">
+        <v>0</v>
+      </c>
+      <c r="F191" t="s">
+        <v>14</v>
+      </c>
+      <c r="H191" t="s">
+        <v>105</v>
+      </c>
+      <c r="I191" t="s">
+        <v>120</v>
+      </c>
+      <c r="J191">
+        <v>2</v>
+      </c>
+      <c r="K191">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="192" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A192" t="s">
+        <v>31</v>
+      </c>
+      <c r="B192" t="s">
+        <v>24</v>
+      </c>
+      <c r="C192" t="s">
+        <v>125</v>
+      </c>
+      <c r="D192" t="s">
+        <v>19</v>
+      </c>
+      <c r="E192" t="b">
+        <v>0</v>
+      </c>
+      <c r="F192" t="s">
+        <v>14</v>
+      </c>
+      <c r="H192" t="s">
+        <v>105</v>
+      </c>
+      <c r="I192" t="s">
+        <v>120</v>
+      </c>
+      <c r="J192">
+        <v>2</v>
+      </c>
+      <c r="K192">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="193" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A193" t="s">
+        <v>20</v>
+      </c>
+      <c r="B193" t="s">
+        <v>11</v>
+      </c>
+      <c r="C193" t="s">
+        <v>126</v>
+      </c>
+      <c r="D193" t="s">
+        <v>19</v>
+      </c>
+      <c r="E193" t="b">
+        <v>0</v>
+      </c>
+      <c r="F193" t="s">
+        <v>14</v>
+      </c>
+      <c r="H193" t="s">
+        <v>105</v>
+      </c>
+      <c r="I193" t="s">
+        <v>120</v>
+      </c>
+      <c r="J193">
+        <v>2</v>
+      </c>
+      <c r="K193">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="194" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A194" t="s">
+        <v>29</v>
+      </c>
+      <c r="B194" t="s">
+        <v>13</v>
+      </c>
+      <c r="C194" t="s">
+        <v>127</v>
+      </c>
+      <c r="D194" t="s">
+        <v>11</v>
+      </c>
+      <c r="E194" t="b">
+        <v>0</v>
+      </c>
+      <c r="F194" t="s">
+        <v>14</v>
+      </c>
+      <c r="H194" t="s">
+        <v>105</v>
+      </c>
+      <c r="I194" t="s">
+        <v>120</v>
+      </c>
+      <c r="J194">
+        <v>2</v>
+      </c>
+      <c r="K194">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="195" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A195" t="s">
+        <v>10</v>
+      </c>
+      <c r="B195" t="s">
+        <v>11</v>
+      </c>
+      <c r="C195" t="s">
+        <v>128</v>
+      </c>
+      <c r="D195" t="s">
+        <v>13</v>
+      </c>
+      <c r="E195" t="b">
+        <v>0</v>
+      </c>
+      <c r="F195" t="s">
+        <v>14</v>
+      </c>
+      <c r="H195" t="s">
+        <v>105</v>
+      </c>
+      <c r="I195" t="s">
+        <v>120</v>
+      </c>
+      <c r="J195">
+        <v>2</v>
+      </c>
+      <c r="K195">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="196" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A196" t="s">
+        <v>77</v>
+      </c>
+      <c r="B196" t="s">
+        <v>13</v>
+      </c>
+      <c r="C196" t="s">
+        <v>131</v>
+      </c>
+      <c r="D196" t="s">
+        <v>19</v>
+      </c>
+      <c r="E196" t="b">
+        <v>0</v>
+      </c>
+      <c r="F196" t="s">
+        <v>14</v>
+      </c>
+      <c r="H196" t="s">
+        <v>105</v>
+      </c>
+      <c r="I196" t="s">
+        <v>129</v>
+      </c>
+      <c r="J196">
+        <v>3</v>
+      </c>
+      <c r="K196">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="197" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A197" t="s">
+        <v>132</v>
+      </c>
+      <c r="B197" t="s">
+        <v>24</v>
+      </c>
+      <c r="C197" t="s">
+        <v>133</v>
+      </c>
+      <c r="D197" t="s">
+        <v>11</v>
+      </c>
+      <c r="E197" t="b">
+        <v>0</v>
+      </c>
+      <c r="F197" t="s">
+        <v>14</v>
+      </c>
+      <c r="H197" t="s">
+        <v>105</v>
+      </c>
+      <c r="I197" t="s">
+        <v>129</v>
+      </c>
+      <c r="J197">
+        <v>3</v>
+      </c>
+      <c r="K197">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="198" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A198" t="s">
+        <v>31</v>
+      </c>
+      <c r="B198" t="s">
+        <v>24</v>
+      </c>
+      <c r="C198" t="s">
+        <v>134</v>
+      </c>
+      <c r="D198" t="s">
+        <v>19</v>
+      </c>
+      <c r="E198" t="b">
+        <v>0</v>
+      </c>
+      <c r="F198" t="s">
+        <v>14</v>
+      </c>
+      <c r="H198" t="s">
+        <v>105</v>
+      </c>
+      <c r="I198" t="s">
+        <v>129</v>
+      </c>
+      <c r="J198">
+        <v>3</v>
+      </c>
+      <c r="K198">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="199" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A199" t="s">
+        <v>110</v>
+      </c>
+      <c r="B199" t="s">
+        <v>13</v>
+      </c>
+      <c r="C199" t="s">
+        <v>135</v>
+      </c>
+      <c r="D199" t="s">
+        <v>11</v>
+      </c>
+      <c r="E199" t="b">
+        <v>0</v>
+      </c>
+      <c r="F199" t="s">
+        <v>14</v>
+      </c>
+      <c r="H199" t="s">
+        <v>105</v>
+      </c>
+      <c r="I199" t="s">
+        <v>129</v>
+      </c>
+      <c r="J199">
+        <v>3</v>
+      </c>
+      <c r="K199">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="200" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A200" t="s">
+        <v>25</v>
+      </c>
+      <c r="B200" t="s">
+        <v>13</v>
+      </c>
+      <c r="C200" t="s">
+        <v>136</v>
+      </c>
+      <c r="D200" t="s">
+        <v>24</v>
+      </c>
+      <c r="E200" t="b">
+        <v>0</v>
+      </c>
+      <c r="F200" t="s">
+        <v>14</v>
+      </c>
+      <c r="H200" t="s">
+        <v>105</v>
+      </c>
+      <c r="I200" t="s">
+        <v>129</v>
+      </c>
+      <c r="J200">
+        <v>3</v>
+      </c>
+      <c r="K200">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="201" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A201" t="s">
+        <v>20</v>
+      </c>
+      <c r="B201" t="s">
+        <v>11</v>
+      </c>
+      <c r="C201" t="s">
+        <v>137</v>
+      </c>
+      <c r="D201" t="s">
+        <v>19</v>
+      </c>
+      <c r="E201" t="b">
+        <v>0</v>
+      </c>
+      <c r="F201" t="s">
+        <v>14</v>
+      </c>
+      <c r="H201" t="s">
+        <v>105</v>
+      </c>
+      <c r="I201" t="s">
+        <v>129</v>
+      </c>
+      <c r="J201">
+        <v>3</v>
+      </c>
+      <c r="K201">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="202" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A202" t="s">
+        <v>113</v>
+      </c>
+      <c r="B202" t="s">
+        <v>24</v>
+      </c>
+      <c r="C202" t="s">
+        <v>138</v>
+      </c>
+      <c r="D202" t="s">
+        <v>11</v>
+      </c>
+      <c r="E202" t="b">
+        <v>0</v>
+      </c>
+      <c r="F202" t="s">
+        <v>14</v>
+      </c>
+      <c r="H202" t="s">
+        <v>105</v>
+      </c>
+      <c r="I202" t="s">
+        <v>129</v>
+      </c>
+      <c r="J202">
+        <v>3</v>
+      </c>
+      <c r="K202">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="203" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A203" t="s">
+        <v>29</v>
+      </c>
+      <c r="B203" t="s">
+        <v>13</v>
+      </c>
+      <c r="C203" t="s">
+        <v>115</v>
+      </c>
+      <c r="D203" t="s">
+        <v>11</v>
+      </c>
+      <c r="E203" t="b">
+        <v>0</v>
+      </c>
+      <c r="F203" t="s">
+        <v>14</v>
+      </c>
+      <c r="H203" t="s">
+        <v>105</v>
+      </c>
+      <c r="I203" t="s">
+        <v>129</v>
+      </c>
+      <c r="J203">
+        <v>3</v>
+      </c>
+      <c r="K203">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="204" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A204" t="s">
+        <v>10</v>
+      </c>
+      <c r="B204" t="s">
+        <v>11</v>
+      </c>
+      <c r="C204" t="s">
+        <v>139</v>
+      </c>
+      <c r="D204" t="s">
+        <v>13</v>
+      </c>
+      <c r="E204" t="b">
+        <v>0</v>
+      </c>
+      <c r="F204" t="s">
+        <v>14</v>
+      </c>
+      <c r="H204" t="s">
+        <v>105</v>
+      </c>
+      <c r="I204" t="s">
+        <v>129</v>
+      </c>
+      <c r="J204">
+        <v>3</v>
+      </c>
+      <c r="K204">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="205" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A205" t="s">
+        <v>25</v>
+      </c>
+      <c r="B205" t="s">
+        <v>13</v>
+      </c>
+      <c r="C205" t="s">
+        <v>140</v>
+      </c>
+      <c r="D205" t="s">
+        <v>24</v>
+      </c>
+      <c r="E205" t="b">
+        <v>0</v>
+      </c>
+      <c r="F205" t="s">
+        <v>14</v>
+      </c>
+      <c r="H205" t="s">
+        <v>105</v>
+      </c>
+      <c r="I205" t="s">
+        <v>141</v>
+      </c>
+      <c r="J205">
+        <v>4</v>
+      </c>
+      <c r="K205">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="206" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A206" t="s">
+        <v>27</v>
+      </c>
+      <c r="B206" t="s">
+        <v>19</v>
+      </c>
+      <c r="C206" t="s">
+        <v>142</v>
+      </c>
+      <c r="D206" t="s">
+        <v>11</v>
+      </c>
+      <c r="E206" t="b">
+        <v>0</v>
+      </c>
+      <c r="F206" t="s">
+        <v>14</v>
+      </c>
+      <c r="H206" t="s">
+        <v>105</v>
+      </c>
+      <c r="I206" t="s">
+        <v>141</v>
+      </c>
+      <c r="J206">
+        <v>4</v>
+      </c>
+      <c r="K206">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="207" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A207" t="s">
+        <v>33</v>
+      </c>
+      <c r="B207" t="s">
+        <v>11</v>
+      </c>
+      <c r="C207" t="s">
+        <v>118</v>
+      </c>
+      <c r="D207" t="s">
+        <v>13</v>
+      </c>
+      <c r="E207" t="b">
+        <v>0</v>
+      </c>
+      <c r="F207" t="s">
+        <v>14</v>
+      </c>
+      <c r="H207" t="s">
+        <v>105</v>
+      </c>
+      <c r="I207" t="s">
+        <v>141</v>
+      </c>
+      <c r="J207">
+        <v>4</v>
+      </c>
+      <c r="K207">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="208" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A208" t="s">
+        <v>17</v>
+      </c>
+      <c r="B208" t="s">
+        <v>11</v>
+      </c>
+      <c r="C208" t="s">
+        <v>143</v>
+      </c>
+      <c r="D208" t="s">
+        <v>19</v>
+      </c>
+      <c r="E208" t="b">
+        <v>0</v>
+      </c>
+      <c r="F208" t="s">
+        <v>14</v>
+      </c>
+      <c r="H208" t="s">
+        <v>105</v>
+      </c>
+      <c r="I208" t="s">
+        <v>141</v>
+      </c>
+      <c r="J208">
+        <v>4</v>
+      </c>
+      <c r="K208">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="209" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A209" t="s">
+        <v>77</v>
+      </c>
+      <c r="B209" t="s">
+        <v>13</v>
+      </c>
+      <c r="C209" t="s">
+        <v>144</v>
+      </c>
+      <c r="D209" t="s">
+        <v>19</v>
+      </c>
+      <c r="E209" t="b">
+        <v>0</v>
+      </c>
+      <c r="F209" t="s">
+        <v>14</v>
+      </c>
+      <c r="H209" t="s">
+        <v>105</v>
+      </c>
+      <c r="I209" t="s">
+        <v>141</v>
+      </c>
+      <c r="J209">
+        <v>4</v>
+      </c>
+      <c r="K209">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="210" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A210" t="s">
+        <v>31</v>
+      </c>
+      <c r="B210" t="s">
+        <v>24</v>
+      </c>
+      <c r="C210" t="s">
+        <v>145</v>
+      </c>
+      <c r="D210" t="s">
+        <v>19</v>
+      </c>
+      <c r="E210" t="b">
+        <v>0</v>
+      </c>
+      <c r="F210" t="s">
+        <v>14</v>
+      </c>
+      <c r="H210" t="s">
+        <v>105</v>
+      </c>
+      <c r="I210" t="s">
+        <v>141</v>
+      </c>
+      <c r="J210">
+        <v>4</v>
+      </c>
+      <c r="K210">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="211" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A211" t="s">
+        <v>20</v>
+      </c>
+      <c r="B211" t="s">
+        <v>11</v>
+      </c>
+      <c r="C211" t="s">
+        <v>146</v>
+      </c>
+      <c r="D211" t="s">
+        <v>19</v>
+      </c>
+      <c r="E211" t="b">
+        <v>0</v>
+      </c>
+      <c r="F211" t="s">
+        <v>14</v>
+      </c>
+      <c r="H211" t="s">
+        <v>105</v>
+      </c>
+      <c r="I211" t="s">
+        <v>141</v>
+      </c>
+      <c r="J211">
+        <v>4</v>
+      </c>
+      <c r="K211">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="212" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A212" t="s">
+        <v>29</v>
+      </c>
+      <c r="B212" t="s">
+        <v>13</v>
+      </c>
+      <c r="C212" t="s">
+        <v>30</v>
+      </c>
+      <c r="D212" t="s">
+        <v>11</v>
+      </c>
+      <c r="E212" t="b">
+        <v>0</v>
+      </c>
+      <c r="F212" t="s">
+        <v>14</v>
+      </c>
+      <c r="H212" t="s">
+        <v>105</v>
+      </c>
+      <c r="I212" t="s">
+        <v>141</v>
+      </c>
+      <c r="J212">
+        <v>4</v>
+      </c>
+      <c r="K212">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="213" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A213" t="s">
+        <v>10</v>
+      </c>
+      <c r="B213" t="s">
+        <v>11</v>
+      </c>
+      <c r="C213" t="s">
+        <v>147</v>
+      </c>
+      <c r="D213" t="s">
+        <v>13</v>
+      </c>
+      <c r="E213" t="b">
+        <v>0</v>
+      </c>
+      <c r="F213" t="s">
+        <v>14</v>
+      </c>
+      <c r="H213" t="s">
+        <v>105</v>
+      </c>
+      <c r="I213" t="s">
+        <v>141</v>
+      </c>
+      <c r="J213">
+        <v>4</v>
+      </c>
+      <c r="K213">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="214" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A214" t="s">
+        <v>25</v>
+      </c>
+      <c r="B214" t="s">
+        <v>13</v>
+      </c>
+      <c r="C214" t="s">
+        <v>148</v>
+      </c>
+      <c r="D214" t="s">
+        <v>24</v>
+      </c>
+      <c r="E214" t="b">
+        <v>0</v>
+      </c>
+      <c r="F214" t="s">
+        <v>14</v>
+      </c>
+      <c r="H214" t="s">
+        <v>105</v>
+      </c>
+      <c r="I214" t="s">
+        <v>149</v>
+      </c>
+      <c r="J214">
+        <v>5</v>
+      </c>
+      <c r="K214">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="215" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A215" t="s">
+        <v>27</v>
+      </c>
+      <c r="B215" t="s">
+        <v>19</v>
+      </c>
+      <c r="C215" t="s">
+        <v>150</v>
+      </c>
+      <c r="D215" t="s">
+        <v>11</v>
+      </c>
+      <c r="E215" t="b">
+        <v>0</v>
+      </c>
+      <c r="F215" t="s">
+        <v>14</v>
+      </c>
+      <c r="H215" t="s">
+        <v>105</v>
+      </c>
+      <c r="I215" t="s">
+        <v>149</v>
+      </c>
+      <c r="J215">
+        <v>5</v>
+      </c>
+      <c r="K215">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="216" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A216" t="s">
+        <v>33</v>
+      </c>
+      <c r="B216" t="s">
+        <v>11</v>
+      </c>
+      <c r="C216" t="s">
+        <v>118</v>
+      </c>
+      <c r="D216" t="s">
+        <v>13</v>
+      </c>
+      <c r="E216" t="b">
+        <v>0</v>
+      </c>
+      <c r="F216" t="s">
+        <v>14</v>
+      </c>
+      <c r="H216" t="s">
+        <v>105</v>
+      </c>
+      <c r="I216" t="s">
+        <v>149</v>
+      </c>
+      <c r="J216">
+        <v>5</v>
+      </c>
+      <c r="K216">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="217" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A217" t="s">
+        <v>17</v>
+      </c>
+      <c r="B217" t="s">
+        <v>11</v>
+      </c>
+      <c r="C217" t="s">
+        <v>151</v>
+      </c>
+      <c r="D217" t="s">
+        <v>19</v>
+      </c>
+      <c r="E217" t="b">
+        <v>0</v>
+      </c>
+      <c r="F217" t="s">
+        <v>14</v>
+      </c>
+      <c r="H217" t="s">
+        <v>105</v>
+      </c>
+      <c r="I217" t="s">
+        <v>149</v>
+      </c>
+      <c r="J217">
+        <v>5</v>
+      </c>
+      <c r="K217">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="218" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A218" t="s">
+        <v>77</v>
+      </c>
+      <c r="B218" t="s">
+        <v>13</v>
+      </c>
+      <c r="C218" t="s">
+        <v>152</v>
+      </c>
+      <c r="D218" t="s">
+        <v>19</v>
+      </c>
+      <c r="E218" t="b">
+        <v>0</v>
+      </c>
+      <c r="F218" t="s">
+        <v>14</v>
+      </c>
+      <c r="H218" t="s">
+        <v>105</v>
+      </c>
+      <c r="I218" t="s">
+        <v>149</v>
+      </c>
+      <c r="J218">
+        <v>5</v>
+      </c>
+      <c r="K218">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="219" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A219" t="s">
+        <v>31</v>
+      </c>
+      <c r="B219" t="s">
+        <v>24</v>
+      </c>
+      <c r="C219" t="s">
+        <v>153</v>
+      </c>
+      <c r="D219" t="s">
+        <v>19</v>
+      </c>
+      <c r="E219" t="b">
+        <v>0</v>
+      </c>
+      <c r="F219" t="s">
+        <v>14</v>
+      </c>
+      <c r="H219" t="s">
+        <v>105</v>
+      </c>
+      <c r="I219" t="s">
+        <v>149</v>
+      </c>
+      <c r="J219">
+        <v>5</v>
+      </c>
+      <c r="K219">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="220" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A220" t="s">
+        <v>20</v>
+      </c>
+      <c r="B220" t="s">
+        <v>11</v>
+      </c>
+      <c r="C220" t="s">
+        <v>154</v>
+      </c>
+      <c r="D220" t="s">
+        <v>19</v>
+      </c>
+      <c r="E220" t="b">
+        <v>0</v>
+      </c>
+      <c r="F220" t="s">
+        <v>14</v>
+      </c>
+      <c r="H220" t="s">
+        <v>105</v>
+      </c>
+      <c r="I220" t="s">
+        <v>149</v>
+      </c>
+      <c r="J220">
+        <v>5</v>
+      </c>
+      <c r="K220">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="221" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A221" t="s">
+        <v>29</v>
+      </c>
+      <c r="B221" t="s">
+        <v>13</v>
+      </c>
+      <c r="C221" t="s">
+        <v>115</v>
+      </c>
+      <c r="D221" t="s">
+        <v>11</v>
+      </c>
+      <c r="E221" t="b">
+        <v>0</v>
+      </c>
+      <c r="F221" t="s">
+        <v>14</v>
+      </c>
+      <c r="H221" t="s">
+        <v>105</v>
+      </c>
+      <c r="I221" t="s">
+        <v>149</v>
+      </c>
+      <c r="J221">
+        <v>5</v>
+      </c>
+      <c r="K221">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="222" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A222" t="s">
+        <v>10</v>
+      </c>
+      <c r="B222" t="s">
+        <v>11</v>
+      </c>
+      <c r="C222" t="s">
+        <v>155</v>
+      </c>
+      <c r="D222" t="s">
+        <v>13</v>
+      </c>
+      <c r="E222" t="b">
+        <v>0</v>
+      </c>
+      <c r="F222" t="s">
+        <v>14</v>
+      </c>
+      <c r="H222" t="s">
+        <v>105</v>
+      </c>
+      <c r="I222" t="s">
+        <v>149</v>
+      </c>
+      <c r="J222">
+        <v>5</v>
+      </c>
+      <c r="K222">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="223" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A223" t="s">
+        <v>38</v>
+      </c>
+      <c r="B223" t="s">
+        <v>24</v>
+      </c>
+      <c r="C223" t="s">
+        <v>549</v>
+      </c>
+      <c r="D223" t="s">
+        <v>13</v>
+      </c>
+      <c r="E223" t="b">
+        <v>0</v>
+      </c>
+      <c r="F223" t="s">
+        <v>37</v>
+      </c>
+      <c r="G223">
+        <v>8</v>
+      </c>
+      <c r="H223" t="s">
+        <v>346</v>
+      </c>
+      <c r="I223" t="s">
+        <v>347</v>
+      </c>
+      <c r="J223">
+        <v>0</v>
+      </c>
+      <c r="K223">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="224" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A224" t="s">
+        <v>40</v>
+      </c>
+      <c r="B224" t="s">
+        <v>11</v>
+      </c>
+      <c r="C224" t="s">
+        <v>550</v>
+      </c>
+      <c r="D224" t="s">
+        <v>24</v>
+      </c>
+      <c r="E224" t="b">
+        <v>0</v>
+      </c>
+      <c r="F224" t="s">
+        <v>37</v>
+      </c>
+      <c r="G224">
+        <v>8</v>
+      </c>
+      <c r="H224" t="s">
+        <v>346</v>
+      </c>
+      <c r="I224" t="s">
+        <v>347</v>
+      </c>
+      <c r="J224">
+        <v>0</v>
+      </c>
+      <c r="K224">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="225" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A225" t="s">
+        <v>538</v>
+      </c>
+      <c r="B225" t="s">
+        <v>167</v>
+      </c>
+      <c r="C225" t="s">
+        <v>168</v>
+      </c>
+      <c r="D225" t="s">
+        <v>19</v>
+      </c>
+      <c r="E225" t="b">
+        <v>0</v>
+      </c>
+      <c r="F225" t="s">
+        <v>37</v>
+      </c>
+      <c r="G225">
+        <v>8</v>
+      </c>
+      <c r="H225" t="s">
+        <v>346</v>
+      </c>
+      <c r="I225" t="s">
+        <v>347</v>
+      </c>
+      <c r="J225">
+        <v>0</v>
+      </c>
+      <c r="K225">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="226" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A226" t="s">
+        <v>51</v>
+      </c>
+      <c r="B226" t="s">
+        <v>11</v>
+      </c>
+      <c r="C226" t="s">
+        <v>667</v>
+      </c>
+      <c r="D226" t="s">
+        <v>13</v>
+      </c>
+      <c r="E226" t="b">
+        <v>0</v>
+      </c>
+      <c r="F226" t="s">
+        <v>44</v>
+      </c>
+      <c r="G226">
+        <v>8</v>
+      </c>
+      <c r="H226" t="s">
+        <v>346</v>
+      </c>
+      <c r="I226" t="s">
+        <v>347</v>
+      </c>
+      <c r="J226">
+        <v>0</v>
+      </c>
+      <c r="K226">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="227" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A227" t="s">
+        <v>59</v>
+      </c>
+      <c r="B227" t="s">
+        <v>11</v>
+      </c>
+      <c r="C227" t="s">
+        <v>668</v>
+      </c>
+      <c r="D227" t="s">
+        <v>13</v>
+      </c>
+      <c r="E227" t="b">
+        <v>0</v>
+      </c>
+      <c r="F227" t="s">
+        <v>44</v>
+      </c>
+      <c r="G227">
+        <v>8</v>
+      </c>
+      <c r="H227" t="s">
+        <v>346</v>
+      </c>
+      <c r="I227" t="s">
+        <v>347</v>
+      </c>
+      <c r="J227">
+        <v>0</v>
+      </c>
+      <c r="K227">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="228" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A228" t="s">
+        <v>49</v>
+      </c>
+      <c r="B228" t="s">
+        <v>19</v>
+      </c>
+      <c r="C228" t="s">
+        <v>669</v>
+      </c>
+      <c r="D228" t="s">
+        <v>24</v>
+      </c>
+      <c r="E228" t="b">
+        <v>0</v>
+      </c>
+      <c r="F228" t="s">
+        <v>44</v>
+      </c>
+      <c r="G228">
+        <v>8</v>
+      </c>
+      <c r="H228" t="s">
+        <v>346</v>
+      </c>
+      <c r="I228" t="s">
+        <v>347</v>
+      </c>
+      <c r="J228">
+        <v>0</v>
+      </c>
+      <c r="K228">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="229" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A229" t="s">
+        <v>65</v>
+      </c>
+      <c r="B229" t="s">
+        <v>11</v>
+      </c>
+      <c r="C229" t="s">
+        <v>670</v>
+      </c>
+      <c r="D229" t="s">
+        <v>13</v>
+      </c>
+      <c r="E229" t="b">
+        <v>0</v>
+      </c>
+      <c r="F229" t="s">
+        <v>44</v>
+      </c>
+      <c r="G229">
+        <v>8</v>
+      </c>
+      <c r="H229" t="s">
+        <v>346</v>
+      </c>
+      <c r="I229" t="s">
+        <v>347</v>
+      </c>
+      <c r="J229">
+        <v>0</v>
+      </c>
+      <c r="K229">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="230" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A230" t="s">
+        <v>42</v>
+      </c>
+      <c r="B230" t="s">
+        <v>19</v>
+      </c>
+      <c r="C230" t="s">
+        <v>677</v>
+      </c>
+      <c r="D230" t="s">
+        <v>13</v>
+      </c>
+      <c r="E230" t="b">
+        <v>0</v>
+      </c>
+      <c r="F230" t="s">
+        <v>44</v>
+      </c>
+      <c r="G230">
+        <v>8</v>
+      </c>
+      <c r="H230" t="s">
+        <v>346</v>
+      </c>
+      <c r="I230" t="s">
+        <v>347</v>
+      </c>
+      <c r="J230">
+        <v>0</v>
+      </c>
+      <c r="K230">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="231" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A231" t="s">
+        <v>45</v>
+      </c>
+      <c r="B231" t="s">
+        <v>19</v>
+      </c>
+      <c r="C231" t="s">
+        <v>678</v>
+      </c>
+      <c r="D231" t="s">
+        <v>13</v>
+      </c>
+      <c r="E231" t="b">
+        <v>0</v>
+      </c>
+      <c r="F231" t="s">
+        <v>44</v>
+      </c>
+      <c r="G231">
+        <v>8</v>
+      </c>
+      <c r="H231" t="s">
+        <v>346</v>
+      </c>
+      <c r="I231" t="s">
+        <v>347</v>
+      </c>
+      <c r="J231">
+        <v>0</v>
+      </c>
+      <c r="K231">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="232" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A232" t="s">
+        <v>61</v>
+      </c>
+      <c r="B232" t="s">
+        <v>19</v>
+      </c>
+      <c r="C232" t="s">
+        <v>679</v>
+      </c>
+      <c r="D232" t="s">
+        <v>24</v>
+      </c>
+      <c r="E232" t="b">
+        <v>0</v>
+      </c>
+      <c r="F232" t="s">
+        <v>44</v>
+      </c>
+      <c r="G232">
+        <v>8</v>
+      </c>
+      <c r="H232" t="s">
+        <v>346</v>
+      </c>
+      <c r="I232" t="s">
+        <v>347</v>
+      </c>
+      <c r="J232">
+        <v>0</v>
+      </c>
+      <c r="K232">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="233" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A233" t="s">
+        <v>649</v>
+      </c>
+      <c r="B233" t="s">
+        <v>19</v>
+      </c>
+      <c r="C233" t="s">
+        <v>680</v>
+      </c>
+      <c r="D233" t="s">
+        <v>24</v>
+      </c>
+      <c r="E233" t="b">
+        <v>0</v>
+      </c>
+      <c r="F233" t="s">
+        <v>44</v>
+      </c>
+      <c r="G233">
+        <v>8</v>
+      </c>
+      <c r="H233" t="s">
+        <v>346</v>
+      </c>
+      <c r="I233" t="s">
+        <v>347</v>
+      </c>
+      <c r="J233">
+        <v>0</v>
+      </c>
+      <c r="K233">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="234" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A234" t="s">
+        <v>409</v>
+      </c>
+      <c r="B234" t="s">
+        <v>24</v>
+      </c>
+      <c r="C234" t="s">
+        <v>508</v>
+      </c>
+      <c r="D234" t="s">
+        <v>19</v>
+      </c>
+      <c r="E234" t="b">
+        <v>0</v>
+      </c>
+      <c r="F234" t="s">
+        <v>14</v>
+      </c>
+      <c r="G234">
+        <v>8</v>
+      </c>
+      <c r="H234" t="s">
+        <v>346</v>
+      </c>
+      <c r="I234" t="s">
+        <v>347</v>
+      </c>
+      <c r="J234">
+        <v>0</v>
+      </c>
+      <c r="K234">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="235" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A235" t="s">
+        <v>31</v>
+      </c>
+      <c r="B235" t="s">
+        <v>24</v>
+      </c>
+      <c r="C235" t="s">
+        <v>509</v>
+      </c>
+      <c r="D235" t="s">
+        <v>19</v>
+      </c>
+      <c r="E235" t="b">
+        <v>0</v>
+      </c>
+      <c r="F235" t="s">
+        <v>14</v>
+      </c>
+      <c r="G235">
+        <v>8</v>
+      </c>
+      <c r="H235" t="s">
+        <v>346</v>
+      </c>
+      <c r="I235" t="s">
+        <v>347</v>
+      </c>
+      <c r="J235">
+        <v>0</v>
+      </c>
+      <c r="K235">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="236" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A236" t="s">
+        <v>368</v>
+      </c>
+      <c r="B236" t="s">
+        <v>24</v>
+      </c>
+      <c r="C236" t="s">
+        <v>510</v>
+      </c>
+      <c r="D236" t="s">
+        <v>11</v>
+      </c>
+      <c r="E236" t="b">
+        <v>0</v>
+      </c>
+      <c r="F236" t="s">
+        <v>14</v>
+      </c>
+      <c r="G236">
+        <v>8</v>
+      </c>
+      <c r="H236" t="s">
+        <v>346</v>
+      </c>
+      <c r="I236" t="s">
+        <v>347</v>
+      </c>
+      <c r="J236">
+        <v>0</v>
+      </c>
+      <c r="K236">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="237" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A237" t="s">
+        <v>27</v>
+      </c>
+      <c r="B237" t="s">
+        <v>19</v>
+      </c>
+      <c r="C237" t="s">
+        <v>511</v>
+      </c>
+      <c r="D237" t="s">
+        <v>11</v>
+      </c>
+      <c r="E237" t="b">
+        <v>0</v>
+      </c>
+      <c r="F237" t="s">
+        <v>14</v>
+      </c>
+      <c r="G237">
+        <v>8</v>
+      </c>
+      <c r="H237" t="s">
+        <v>346</v>
+      </c>
+      <c r="I237" t="s">
+        <v>347</v>
+      </c>
+      <c r="J237">
+        <v>0</v>
+      </c>
+      <c r="K237">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="238" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A238" t="s">
+        <v>132</v>
+      </c>
+      <c r="B238" t="s">
+        <v>24</v>
+      </c>
+      <c r="C238" t="s">
+        <v>512</v>
+      </c>
+      <c r="D238" t="s">
+        <v>11</v>
+      </c>
+      <c r="E238" t="b">
+        <v>0</v>
+      </c>
+      <c r="F238" t="s">
+        <v>14</v>
+      </c>
+      <c r="G238">
+        <v>8</v>
+      </c>
+      <c r="H238" t="s">
+        <v>346</v>
+      </c>
+      <c r="I238" t="s">
+        <v>347</v>
+      </c>
+      <c r="J238">
+        <v>0</v>
+      </c>
+      <c r="K238">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="239" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A239" t="s">
+        <v>365</v>
+      </c>
+      <c r="B239" t="s">
+        <v>24</v>
+      </c>
+      <c r="C239" t="s">
+        <v>516</v>
+      </c>
+      <c r="D239" t="s">
+        <v>19</v>
+      </c>
+      <c r="E239" t="b">
+        <v>0</v>
+      </c>
+      <c r="F239" t="s">
+        <v>14</v>
+      </c>
+      <c r="G239">
+        <v>8</v>
+      </c>
+      <c r="H239" t="s">
+        <v>346</v>
+      </c>
+      <c r="I239" t="s">
+        <v>347</v>
+      </c>
+      <c r="J239">
+        <v>0</v>
+      </c>
+      <c r="K239">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="240" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A240" t="s">
+        <v>350</v>
+      </c>
+      <c r="B240" t="s">
+        <v>24</v>
+      </c>
+      <c r="C240" t="s">
+        <v>517</v>
+      </c>
+      <c r="D240" t="s">
+        <v>19</v>
+      </c>
+      <c r="E240" t="b">
+        <v>0</v>
+      </c>
+      <c r="F240" t="s">
+        <v>14</v>
+      </c>
+      <c r="G240">
+        <v>8</v>
+      </c>
+      <c r="H240" t="s">
+        <v>346</v>
+      </c>
+      <c r="I240" t="s">
+        <v>347</v>
+      </c>
+      <c r="J240">
+        <v>0</v>
+      </c>
+      <c r="K240">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="241" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A241" t="s">
+        <v>110</v>
+      </c>
+      <c r="B241" t="s">
+        <v>24</v>
+      </c>
+      <c r="C241" t="s">
+        <v>518</v>
+      </c>
+      <c r="D241" t="s">
+        <v>11</v>
+      </c>
+      <c r="E241" t="b">
+        <v>0</v>
+      </c>
+      <c r="F241" t="s">
+        <v>14</v>
+      </c>
+      <c r="G241">
+        <v>8</v>
+      </c>
+      <c r="H241" t="s">
+        <v>346</v>
+      </c>
+      <c r="I241" t="s">
+        <v>347</v>
+      </c>
+      <c r="J241">
+        <v>0</v>
+      </c>
+      <c r="K241">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="242" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A242" t="s">
+        <v>33</v>
+      </c>
+      <c r="B242" t="s">
+        <v>11</v>
+      </c>
+      <c r="C242" t="s">
+        <v>519</v>
+      </c>
+      <c r="D242" t="s">
+        <v>13</v>
+      </c>
+      <c r="E242" t="b">
+        <v>0</v>
+      </c>
+      <c r="F242" t="s">
+        <v>14</v>
+      </c>
+      <c r="G242">
+        <v>8</v>
+      </c>
+      <c r="H242" t="s">
+        <v>346</v>
+      </c>
+      <c r="I242" t="s">
+        <v>347</v>
+      </c>
+      <c r="J242">
+        <v>0</v>
+      </c>
+      <c r="K242">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="243" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A243" t="s">
+        <v>38</v>
+      </c>
+      <c r="B243" t="s">
+        <v>24</v>
+      </c>
+      <c r="C243" t="s">
+        <v>532</v>
+      </c>
+      <c r="D243" t="s">
+        <v>13</v>
+      </c>
+      <c r="E243" t="b">
+        <v>0</v>
+      </c>
+      <c r="F243" t="s">
+        <v>37</v>
+      </c>
+      <c r="G243">
+        <v>3</v>
+      </c>
+      <c r="H243" t="s">
+        <v>346</v>
+      </c>
+      <c r="I243" t="s">
+        <v>347</v>
+      </c>
+      <c r="J243">
+        <v>0</v>
+      </c>
+      <c r="K243">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="244" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A244" t="s">
+        <v>40</v>
+      </c>
+      <c r="B244" t="s">
+        <v>11</v>
+      </c>
+      <c r="C244" t="s">
+        <v>533</v>
+      </c>
+      <c r="D244" t="s">
+        <v>24</v>
+      </c>
+      <c r="E244" t="b">
+        <v>0</v>
+      </c>
+      <c r="F244" t="s">
+        <v>37</v>
+      </c>
+      <c r="G244">
+        <v>3</v>
+      </c>
+      <c r="H244" t="s">
+        <v>346</v>
+      </c>
+      <c r="I244" t="s">
+        <v>347</v>
+      </c>
+      <c r="J244">
+        <v>0</v>
+      </c>
+      <c r="K244">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="245" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A245" t="s">
+        <v>83</v>
+      </c>
+      <c r="B245" t="s">
+        <v>11</v>
+      </c>
+      <c r="C245" t="s">
+        <v>534</v>
+      </c>
+      <c r="D245" t="s">
+        <v>19</v>
+      </c>
+      <c r="E245" t="b">
+        <v>0</v>
+      </c>
+      <c r="F245" t="s">
+        <v>37</v>
+      </c>
+      <c r="G245">
+        <v>3</v>
+      </c>
+      <c r="H245" t="s">
+        <v>346</v>
+      </c>
+      <c r="I245" t="s">
+        <v>347</v>
+      </c>
+      <c r="J245">
+        <v>0</v>
+      </c>
+      <c r="K245">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="246" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A246" t="s">
+        <v>560</v>
+      </c>
+      <c r="B246" t="s">
+        <v>19</v>
+      </c>
+      <c r="C246" t="s">
+        <v>586</v>
+      </c>
+      <c r="D246" t="s">
+        <v>24</v>
+      </c>
+      <c r="E246" t="b">
+        <v>0</v>
+      </c>
+      <c r="F246" t="s">
+        <v>44</v>
+      </c>
+      <c r="G246">
+        <v>3</v>
+      </c>
+      <c r="H246" t="s">
+        <v>346</v>
+      </c>
+      <c r="I246" t="s">
+        <v>347</v>
+      </c>
+      <c r="J246">
+        <v>0</v>
+      </c>
+      <c r="K246">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="247" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A247" t="s">
+        <v>587</v>
+      </c>
+      <c r="B247" t="s">
+        <v>19</v>
+      </c>
+      <c r="C247" t="s">
+        <v>588</v>
+      </c>
+      <c r="D247" t="s">
+        <v>13</v>
+      </c>
+      <c r="E247" t="b">
+        <v>0</v>
+      </c>
+      <c r="F247" t="s">
+        <v>44</v>
+      </c>
+      <c r="G247">
+        <v>3</v>
+      </c>
+      <c r="H247" t="s">
+        <v>346</v>
+      </c>
+      <c r="I247" t="s">
+        <v>347</v>
+      </c>
+      <c r="J247">
+        <v>0</v>
+      </c>
+      <c r="K247">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="248" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A248" t="s">
+        <v>42</v>
+      </c>
+      <c r="B248" t="s">
+        <v>19</v>
+      </c>
+      <c r="C248" t="s">
+        <v>589</v>
+      </c>
+      <c r="D248" t="s">
+        <v>13</v>
+      </c>
+      <c r="E248" t="b">
+        <v>0</v>
+      </c>
+      <c r="F248" t="s">
+        <v>44</v>
+      </c>
+      <c r="G248">
+        <v>3</v>
+      </c>
+      <c r="H248" t="s">
+        <v>346</v>
+      </c>
+      <c r="I248" t="s">
+        <v>347</v>
+      </c>
+      <c r="J248">
+        <v>0</v>
+      </c>
+      <c r="K248">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="249" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A249" t="s">
+        <v>49</v>
+      </c>
+      <c r="B249" t="s">
+        <v>19</v>
+      </c>
+      <c r="C249" t="s">
+        <v>590</v>
+      </c>
+      <c r="D249" t="s">
+        <v>24</v>
+      </c>
+      <c r="E249" t="b">
+        <v>0</v>
+      </c>
+      <c r="F249" t="s">
+        <v>44</v>
+      </c>
+      <c r="G249">
+        <v>3</v>
+      </c>
+      <c r="H249" t="s">
+        <v>346</v>
+      </c>
+      <c r="I249" t="s">
+        <v>347</v>
+      </c>
+      <c r="J249">
+        <v>0</v>
+      </c>
+      <c r="K249">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="250" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A250" t="s">
+        <v>59</v>
+      </c>
+      <c r="B250" t="s">
+        <v>11</v>
+      </c>
+      <c r="C250" t="s">
+        <v>595</v>
+      </c>
+      <c r="D250" t="s">
+        <v>13</v>
+      </c>
+      <c r="E250" t="b">
+        <v>0</v>
+      </c>
+      <c r="F250" t="s">
+        <v>44</v>
+      </c>
+      <c r="G250">
+        <v>3</v>
+      </c>
+      <c r="H250" t="s">
+        <v>346</v>
+      </c>
+      <c r="I250" t="s">
+        <v>347</v>
+      </c>
+      <c r="J250">
+        <v>0</v>
+      </c>
+      <c r="K250">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="251" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A251" t="s">
+        <v>61</v>
+      </c>
+      <c r="B251" t="s">
+        <v>19</v>
+      </c>
+      <c r="C251" t="s">
+        <v>596</v>
+      </c>
+      <c r="D251" t="s">
+        <v>24</v>
+      </c>
+      <c r="E251" t="b">
+        <v>0</v>
+      </c>
+      <c r="F251" t="s">
+        <v>44</v>
+      </c>
+      <c r="G251">
+        <v>3</v>
+      </c>
+      <c r="H251" t="s">
+        <v>346</v>
+      </c>
+      <c r="I251" t="s">
+        <v>347</v>
+      </c>
+      <c r="J251">
+        <v>0</v>
+      </c>
+      <c r="K251">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="252" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A252" t="s">
+        <v>53</v>
+      </c>
+      <c r="B252" t="s">
+        <v>11</v>
+      </c>
+      <c r="C252" t="s">
+        <v>597</v>
+      </c>
+      <c r="D252" t="s">
+        <v>24</v>
+      </c>
+      <c r="E252" t="b">
+        <v>0</v>
+      </c>
+      <c r="F252" t="s">
+        <v>44</v>
+      </c>
+      <c r="G252">
+        <v>3</v>
+      </c>
+      <c r="H252" t="s">
+        <v>346</v>
+      </c>
+      <c r="I252" t="s">
+        <v>347</v>
+      </c>
+      <c r="J252">
+        <v>0</v>
+      </c>
+      <c r="K252">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="253" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A253" t="s">
+        <v>51</v>
+      </c>
+      <c r="B253" t="s">
+        <v>11</v>
+      </c>
+      <c r="C253" t="s">
+        <v>598</v>
+      </c>
+      <c r="D253" t="s">
+        <v>13</v>
+      </c>
+      <c r="E253" t="b">
+        <v>0</v>
+      </c>
+      <c r="F253" t="s">
+        <v>44</v>
+      </c>
+      <c r="G253">
+        <v>3</v>
+      </c>
+      <c r="H253" t="s">
+        <v>346</v>
+      </c>
+      <c r="I253" t="s">
+        <v>347</v>
+      </c>
+      <c r="J253">
+        <v>0</v>
+      </c>
+      <c r="K253">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="254" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A254" t="s">
+        <v>33</v>
+      </c>
+      <c r="B254" t="s">
+        <v>11</v>
+      </c>
+      <c r="C254" t="s">
+        <v>408</v>
+      </c>
+      <c r="D254" t="s">
+        <v>13</v>
+      </c>
+      <c r="E254" t="b">
+        <v>0</v>
+      </c>
+      <c r="F254" t="s">
+        <v>14</v>
+      </c>
+      <c r="G254">
+        <v>3</v>
+      </c>
+      <c r="H254" t="s">
+        <v>346</v>
+      </c>
+      <c r="I254" t="s">
+        <v>347</v>
+      </c>
+      <c r="J254">
+        <v>0</v>
+      </c>
+      <c r="K254">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="255" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A255" t="s">
+        <v>409</v>
+      </c>
+      <c r="B255" t="s">
+        <v>24</v>
+      </c>
+      <c r="C255" t="s">
+        <v>410</v>
+      </c>
+      <c r="D255" t="s">
+        <v>19</v>
+      </c>
+      <c r="E255" t="b">
+        <v>0</v>
+      </c>
+      <c r="F255" t="s">
+        <v>14</v>
+      </c>
+      <c r="G255">
+        <v>3</v>
+      </c>
+      <c r="H255" t="s">
+        <v>346</v>
+      </c>
+      <c r="I255" t="s">
+        <v>347</v>
+      </c>
+      <c r="J255">
+        <v>0</v>
+      </c>
+      <c r="K255">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="256" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A256" t="s">
+        <v>365</v>
+      </c>
+      <c r="B256" t="s">
+        <v>13</v>
+      </c>
+      <c r="C256" t="s">
+        <v>411</v>
+      </c>
+      <c r="D256" t="s">
+        <v>19</v>
+      </c>
+      <c r="E256" t="b">
+        <v>0</v>
+      </c>
+      <c r="F256" t="s">
+        <v>14</v>
+      </c>
+      <c r="G256">
+        <v>3</v>
+      </c>
+      <c r="H256" t="s">
+        <v>346</v>
+      </c>
+      <c r="I256" t="s">
+        <v>347</v>
+      </c>
+      <c r="J256">
+        <v>0</v>
+      </c>
+      <c r="K256">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="257" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A257" t="s">
+        <v>113</v>
+      </c>
+      <c r="B257" t="s">
+        <v>24</v>
+      </c>
+      <c r="C257" t="s">
+        <v>412</v>
+      </c>
+      <c r="D257" t="s">
+        <v>11</v>
+      </c>
+      <c r="E257" t="b">
+        <v>0</v>
+      </c>
+      <c r="F257" t="s">
+        <v>14</v>
+      </c>
+      <c r="G257">
+        <v>3</v>
+      </c>
+      <c r="H257" t="s">
+        <v>346</v>
+      </c>
+      <c r="I257" t="s">
+        <v>347</v>
+      </c>
+      <c r="J257">
+        <v>0</v>
+      </c>
+      <c r="K257">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="258" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A258" t="s">
+        <v>387</v>
+      </c>
+      <c r="B258" t="s">
+        <v>24</v>
+      </c>
+      <c r="C258" t="s">
+        <v>413</v>
+      </c>
+      <c r="D258" t="s">
+        <v>13</v>
+      </c>
+      <c r="E258" t="b">
+        <v>0</v>
+      </c>
+      <c r="F258" t="s">
+        <v>14</v>
+      </c>
+      <c r="G258">
+        <v>3</v>
+      </c>
+      <c r="H258" t="s">
+        <v>346</v>
+      </c>
+      <c r="I258" t="s">
+        <v>347</v>
+      </c>
+      <c r="J258">
+        <v>0</v>
+      </c>
+      <c r="K258">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="259" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A259" t="s">
+        <v>17</v>
+      </c>
+      <c r="B259" t="s">
+        <v>24</v>
+      </c>
+      <c r="C259" t="s">
+        <v>395</v>
+      </c>
+      <c r="D259" t="s">
+        <v>19</v>
+      </c>
+      <c r="E259" t="b">
+        <v>0</v>
+      </c>
+      <c r="F259" t="s">
+        <v>14</v>
+      </c>
+      <c r="G259">
+        <v>3</v>
+      </c>
+      <c r="H259" t="s">
+        <v>346</v>
+      </c>
+      <c r="I259" t="s">
+        <v>347</v>
+      </c>
+      <c r="J259">
+        <v>0</v>
+      </c>
+      <c r="K259">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="260" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A260" t="s">
+        <v>396</v>
+      </c>
+      <c r="B260" t="s">
+        <v>24</v>
+      </c>
+      <c r="C260" t="s">
+        <v>397</v>
+      </c>
+      <c r="D260" t="s">
+        <v>13</v>
+      </c>
+      <c r="E260" t="b">
+        <v>0</v>
+      </c>
+      <c r="F260" t="s">
+        <v>14</v>
+      </c>
+      <c r="G260">
+        <v>3</v>
+      </c>
+      <c r="H260" t="s">
+        <v>346</v>
+      </c>
+      <c r="I260" t="s">
+        <v>347</v>
+      </c>
+      <c r="J260">
+        <v>0</v>
+      </c>
+      <c r="K260">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="261" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A261" t="s">
+        <v>29</v>
+      </c>
+      <c r="B261" t="s">
+        <v>13</v>
+      </c>
+      <c r="C261" t="s">
+        <v>398</v>
+      </c>
+      <c r="D261" t="s">
+        <v>11</v>
+      </c>
+      <c r="E261" t="b">
+        <v>0</v>
+      </c>
+      <c r="F261" t="s">
+        <v>14</v>
+      </c>
+      <c r="G261">
+        <v>3</v>
+      </c>
+      <c r="H261" t="s">
+        <v>346</v>
+      </c>
+      <c r="I261" t="s">
+        <v>347</v>
+      </c>
+      <c r="J261">
+        <v>0</v>
+      </c>
+      <c r="K261">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="262" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A262" t="s">
+        <v>368</v>
+      </c>
+      <c r="B262" t="s">
+        <v>24</v>
+      </c>
+      <c r="C262" t="s">
+        <v>399</v>
+      </c>
+      <c r="D262" t="s">
+        <v>11</v>
+      </c>
+      <c r="E262" t="b">
+        <v>0</v>
+      </c>
+      <c r="F262" t="s">
+        <v>14</v>
+      </c>
+      <c r="G262">
+        <v>3</v>
+      </c>
+      <c r="H262" t="s">
+        <v>346</v>
+      </c>
+      <c r="I262" t="s">
+        <v>347</v>
+      </c>
+      <c r="J262">
+        <v>0</v>
+      </c>
+      <c r="K262">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="263" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A263" t="s">
+        <v>40</v>
+      </c>
+      <c r="B263" t="s">
+        <v>11</v>
+      </c>
+      <c r="C263" t="s">
+        <v>842</v>
+      </c>
+      <c r="D263" t="s">
+        <v>24</v>
+      </c>
+      <c r="E263" t="b">
+        <v>0</v>
+      </c>
+      <c r="F263" t="s">
+        <v>37</v>
+      </c>
+      <c r="G263">
+        <v>3</v>
+      </c>
+      <c r="H263" t="s">
+        <v>682</v>
+      </c>
+      <c r="I263" t="s">
+        <v>683</v>
+      </c>
+      <c r="J263">
+        <v>0</v>
+      </c>
+      <c r="K263">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="264" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A264" t="s">
+        <v>490</v>
+      </c>
+      <c r="B264" t="s">
+        <v>19</v>
+      </c>
+      <c r="C264" t="s">
+        <v>712</v>
+      </c>
+      <c r="D264" t="s">
+        <v>11</v>
+      </c>
+      <c r="E264" t="b">
+        <v>0</v>
+      </c>
+      <c r="F264" t="s">
+        <v>14</v>
+      </c>
+      <c r="G264">
+        <v>3</v>
+      </c>
+      <c r="H264" t="s">
+        <v>682</v>
+      </c>
+      <c r="I264" t="s">
+        <v>683</v>
+      </c>
+      <c r="J264">
+        <v>0</v>
+      </c>
+      <c r="K264">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="265" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A265" t="s">
+        <v>77</v>
+      </c>
+      <c r="B265" t="s">
+        <v>13</v>
+      </c>
+      <c r="C265" t="s">
+        <v>713</v>
+      </c>
+      <c r="D265" t="s">
+        <v>19</v>
+      </c>
+      <c r="E265" t="b">
+        <v>0</v>
+      </c>
+      <c r="F265" t="s">
+        <v>14</v>
+      </c>
+      <c r="G265">
+        <v>3</v>
+      </c>
+      <c r="H265" t="s">
+        <v>682</v>
+      </c>
+      <c r="I265" t="s">
+        <v>683</v>
+      </c>
+      <c r="J265">
+        <v>0</v>
+      </c>
+      <c r="K265">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="266" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A266" t="s">
+        <v>393</v>
+      </c>
+      <c r="B266" t="s">
+        <v>24</v>
+      </c>
+      <c r="C266" t="s">
+        <v>714</v>
+      </c>
+      <c r="D266" t="s">
+        <v>11</v>
+      </c>
+      <c r="E266" t="b">
+        <v>0</v>
+      </c>
+      <c r="F266" t="s">
+        <v>14</v>
+      </c>
+      <c r="G266">
+        <v>3</v>
+      </c>
+      <c r="H266" t="s">
+        <v>682</v>
+      </c>
+      <c r="I266" t="s">
+        <v>683</v>
+      </c>
+      <c r="J266">
+        <v>0</v>
+      </c>
+      <c r="K266">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="267" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A267" t="s">
+        <v>17</v>
+      </c>
+      <c r="B267" t="s">
+        <v>24</v>
+      </c>
+      <c r="C267" t="s">
+        <v>715</v>
+      </c>
+      <c r="D267" t="s">
+        <v>19</v>
+      </c>
+      <c r="E267" t="b">
+        <v>0</v>
+      </c>
+      <c r="F267" t="s">
+        <v>14</v>
+      </c>
+      <c r="G267">
+        <v>3</v>
+      </c>
+      <c r="H267" t="s">
+        <v>682</v>
+      </c>
+      <c r="I267" t="s">
+        <v>683</v>
+      </c>
+      <c r="J267">
+        <v>0</v>
+      </c>
+      <c r="K267">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="268" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A268" t="s">
+        <v>20</v>
+      </c>
+      <c r="B268" t="s">
+        <v>11</v>
+      </c>
+      <c r="C268" t="s">
+        <v>716</v>
+      </c>
+      <c r="D268" t="s">
+        <v>19</v>
+      </c>
+      <c r="E268" t="b">
+        <v>0</v>
+      </c>
+      <c r="F268" t="s">
+        <v>14</v>
+      </c>
+      <c r="G268">
+        <v>3</v>
+      </c>
+      <c r="H268" t="s">
+        <v>682</v>
+      </c>
+      <c r="I268" t="s">
+        <v>683</v>
+      </c>
+      <c r="J268">
+        <v>0</v>
+      </c>
+      <c r="K268">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="269" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A269" t="s">
+        <v>33</v>
+      </c>
+      <c r="B269" t="s">
+        <v>11</v>
+      </c>
+      <c r="C269" t="s">
+        <v>723</v>
+      </c>
+      <c r="D269" t="s">
+        <v>13</v>
+      </c>
+      <c r="E269" t="b">
+        <v>0</v>
+      </c>
+      <c r="F269" t="s">
+        <v>14</v>
+      </c>
+      <c r="G269">
+        <v>3</v>
+      </c>
+      <c r="H269" t="s">
+        <v>682</v>
+      </c>
+      <c r="I269" t="s">
+        <v>683</v>
+      </c>
+      <c r="J269">
+        <v>0</v>
+      </c>
+      <c r="K269">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="270" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A270" t="s">
+        <v>353</v>
+      </c>
+      <c r="B270" t="s">
+        <v>24</v>
+      </c>
+      <c r="C270" t="s">
+        <v>724</v>
+      </c>
+      <c r="D270" t="s">
+        <v>19</v>
+      </c>
+      <c r="E270" t="b">
+        <v>0</v>
+      </c>
+      <c r="F270" t="s">
+        <v>14</v>
+      </c>
+      <c r="G270">
+        <v>3</v>
+      </c>
+      <c r="H270" t="s">
+        <v>682</v>
+      </c>
+      <c r="I270" t="s">
+        <v>683</v>
+      </c>
+      <c r="J270">
+        <v>0</v>
+      </c>
+      <c r="K270">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="271" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A271" t="s">
+        <v>396</v>
+      </c>
+      <c r="B271" t="s">
+        <v>24</v>
+      </c>
+      <c r="C271" t="s">
+        <v>725</v>
+      </c>
+      <c r="D271" t="s">
+        <v>13</v>
+      </c>
+      <c r="E271" t="b">
+        <v>0</v>
+      </c>
+      <c r="F271" t="s">
+        <v>14</v>
+      </c>
+      <c r="G271">
+        <v>3</v>
+      </c>
+      <c r="H271" t="s">
+        <v>682</v>
+      </c>
+      <c r="I271" t="s">
+        <v>683</v>
+      </c>
+      <c r="J271">
+        <v>0</v>
+      </c>
+      <c r="K271">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="272" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A272" t="s">
+        <v>350</v>
+      </c>
+      <c r="B272" t="s">
+        <v>24</v>
+      </c>
+      <c r="C272" t="s">
+        <v>726</v>
+      </c>
+      <c r="D272" t="s">
+        <v>19</v>
+      </c>
+      <c r="E272" t="b">
+        <v>0</v>
+      </c>
+      <c r="F272" t="s">
+        <v>14</v>
+      </c>
+      <c r="G272">
+        <v>3</v>
+      </c>
+      <c r="H272" t="s">
+        <v>682</v>
+      </c>
+      <c r="I272" t="s">
+        <v>683</v>
+      </c>
+      <c r="J272">
+        <v>0</v>
+      </c>
+      <c r="K272">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="273" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A273" t="s">
+        <v>27</v>
+      </c>
+      <c r="B273" t="s">
+        <v>19</v>
+      </c>
+      <c r="C273" t="s">
+        <v>727</v>
+      </c>
+      <c r="D273" t="s">
+        <v>11</v>
+      </c>
+      <c r="E273" t="b">
+        <v>0</v>
+      </c>
+      <c r="F273" t="s">
+        <v>14</v>
+      </c>
+      <c r="G273">
+        <v>3</v>
+      </c>
+      <c r="H273" t="s">
+        <v>682</v>
+      </c>
+      <c r="I273" t="s">
+        <v>683</v>
+      </c>
+      <c r="J273">
+        <v>0</v>
+      </c>
+      <c r="K273">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="274" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A274" t="s">
+        <v>174</v>
+      </c>
+      <c r="B274" t="s">
+        <v>19</v>
+      </c>
+      <c r="C274" t="s">
+        <v>892</v>
+      </c>
+      <c r="D274" t="s">
+        <v>11</v>
+      </c>
+      <c r="E274" t="b">
+        <v>0</v>
+      </c>
+      <c r="F274" t="s">
+        <v>44</v>
+      </c>
+      <c r="G274">
+        <v>3</v>
+      </c>
+      <c r="H274" t="s">
+        <v>682</v>
+      </c>
+      <c r="I274" t="s">
+        <v>683</v>
+      </c>
+      <c r="J274">
+        <v>0</v>
+      </c>
+      <c r="K274">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="275" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A275" t="s">
+        <v>51</v>
+      </c>
+      <c r="B275" t="s">
+        <v>11</v>
+      </c>
+      <c r="C275" t="s">
+        <v>893</v>
+      </c>
+      <c r="D275" t="s">
+        <v>13</v>
+      </c>
+      <c r="E275" t="b">
+        <v>0</v>
+      </c>
+      <c r="F275" t="s">
+        <v>44</v>
+      </c>
+      <c r="G275">
+        <v>3</v>
+      </c>
+      <c r="H275" t="s">
+        <v>682</v>
+      </c>
+      <c r="I275" t="s">
+        <v>683</v>
+      </c>
+      <c r="J275">
+        <v>0</v>
+      </c>
+      <c r="K275">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="276" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A276" t="s">
+        <v>49</v>
+      </c>
+      <c r="B276" t="s">
+        <v>19</v>
+      </c>
+      <c r="C276" t="s">
+        <v>894</v>
+      </c>
+      <c r="D276" t="s">
+        <v>24</v>
+      </c>
+      <c r="E276" t="b">
+        <v>0</v>
+      </c>
+      <c r="F276" t="s">
+        <v>44</v>
+      </c>
+      <c r="G276">
+        <v>3</v>
+      </c>
+      <c r="H276" t="s">
+        <v>682</v>
+      </c>
+      <c r="I276" t="s">
+        <v>683</v>
+      </c>
+      <c r="J276">
+        <v>0</v>
+      </c>
+      <c r="K276">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="277" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A277" t="s">
+        <v>67</v>
+      </c>
+      <c r="B277" t="s">
+        <v>19</v>
+      </c>
+      <c r="C277" t="s">
+        <v>895</v>
+      </c>
+      <c r="D277" t="s">
+        <v>13</v>
+      </c>
+      <c r="E277" t="b">
+        <v>0</v>
+      </c>
+      <c r="F277" t="s">
+        <v>44</v>
+      </c>
+      <c r="G277">
+        <v>3</v>
+      </c>
+      <c r="H277" t="s">
+        <v>682</v>
+      </c>
+      <c r="I277" t="s">
+        <v>683</v>
+      </c>
+      <c r="J277">
+        <v>0</v>
+      </c>
+      <c r="K277">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="278" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A278" t="s">
+        <v>61</v>
+      </c>
+      <c r="B278" t="s">
+        <v>19</v>
+      </c>
+      <c r="C278" t="s">
+        <v>902</v>
+      </c>
+      <c r="D278" t="s">
+        <v>24</v>
+      </c>
+      <c r="E278" t="b">
+        <v>0</v>
+      </c>
+      <c r="F278" t="s">
+        <v>44</v>
+      </c>
+      <c r="G278">
+        <v>3</v>
+      </c>
+      <c r="H278" t="s">
+        <v>682</v>
+      </c>
+      <c r="I278" t="s">
+        <v>683</v>
+      </c>
+      <c r="J278">
+        <v>0</v>
+      </c>
+      <c r="K278">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="279" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A279" t="s">
+        <v>53</v>
+      </c>
+      <c r="B279" t="s">
+        <v>11</v>
+      </c>
+      <c r="C279" t="s">
+        <v>903</v>
+      </c>
+      <c r="D279" t="s">
+        <v>24</v>
+      </c>
+      <c r="E279" t="b">
+        <v>0</v>
+      </c>
+      <c r="F279" t="s">
+        <v>44</v>
+      </c>
+      <c r="G279">
+        <v>3</v>
+      </c>
+      <c r="H279" t="s">
+        <v>682</v>
+      </c>
+      <c r="I279" t="s">
+        <v>683</v>
+      </c>
+      <c r="J279">
+        <v>0</v>
+      </c>
+      <c r="K279">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="280" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A280" t="s">
+        <v>601</v>
+      </c>
+      <c r="B280" t="s">
+        <v>13</v>
+      </c>
+      <c r="C280" t="s">
+        <v>904</v>
+      </c>
+      <c r="D280" t="s">
+        <v>11</v>
+      </c>
+      <c r="E280" t="b">
+        <v>0</v>
+      </c>
+      <c r="F280" t="s">
+        <v>44</v>
+      </c>
+      <c r="G280">
+        <v>3</v>
+      </c>
+      <c r="H280" t="s">
+        <v>682</v>
+      </c>
+      <c r="I280" t="s">
+        <v>683</v>
+      </c>
+      <c r="J280">
+        <v>0</v>
+      </c>
+      <c r="K280">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="281" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A281" t="s">
+        <v>63</v>
+      </c>
+      <c r="B281" t="s">
+        <v>11</v>
+      </c>
+      <c r="C281" t="s">
+        <v>905</v>
+      </c>
+      <c r="D281" t="s">
+        <v>13</v>
+      </c>
+      <c r="E281" t="b">
+        <v>0</v>
+      </c>
+      <c r="F281" t="s">
+        <v>44</v>
+      </c>
+      <c r="G281">
+        <v>3</v>
+      </c>
+      <c r="H281" t="s">
+        <v>682</v>
+      </c>
+      <c r="I281" t="s">
+        <v>683</v>
+      </c>
+      <c r="J281">
+        <v>0</v>
+      </c>
+      <c r="K281">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="282" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A282" t="s">
+        <v>65</v>
+      </c>
+      <c r="B282" t="s">
+        <v>11</v>
+      </c>
+      <c r="C282" t="s">
+        <v>906</v>
+      </c>
+      <c r="D282" t="s">
+        <v>13</v>
+      </c>
+      <c r="E282" t="b">
+        <v>0</v>
+      </c>
+      <c r="F282" t="s">
+        <v>44</v>
+      </c>
+      <c r="G282">
+        <v>3</v>
+      </c>
+      <c r="H282" t="s">
+        <v>682</v>
+      </c>
+      <c r="I282" t="s">
+        <v>683</v>
+      </c>
+      <c r="J282">
+        <v>0</v>
+      </c>
+      <c r="K282">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="283" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A283" t="s">
+        <v>40</v>
+      </c>
+      <c r="B283" t="s">
+        <v>11</v>
+      </c>
+      <c r="C283" t="s">
+        <v>852</v>
+      </c>
+      <c r="D283" t="s">
+        <v>24</v>
+      </c>
+      <c r="E283" t="b">
+        <v>0</v>
+      </c>
+      <c r="F283" t="s">
+        <v>37</v>
+      </c>
+      <c r="G283">
+        <v>8</v>
+      </c>
+      <c r="H283" t="s">
+        <v>682</v>
+      </c>
+      <c r="I283" t="s">
+        <v>683</v>
+      </c>
+      <c r="J283">
+        <v>0</v>
+      </c>
+      <c r="K283">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="284" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A284" t="s">
+        <v>77</v>
+      </c>
+      <c r="B284" t="s">
+        <v>24</v>
+      </c>
+      <c r="C284" t="s">
+        <v>818</v>
+      </c>
+      <c r="D284" t="s">
+        <v>19</v>
+      </c>
+      <c r="E284" t="b">
+        <v>0</v>
+      </c>
+      <c r="F284" t="s">
+        <v>14</v>
+      </c>
+      <c r="G284">
+        <v>8</v>
+      </c>
+      <c r="H284" t="s">
+        <v>682</v>
+      </c>
+      <c r="I284" t="s">
+        <v>683</v>
+      </c>
+      <c r="J284">
+        <v>0</v>
+      </c>
+      <c r="K284">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="285" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A285" t="s">
+        <v>113</v>
+      </c>
+      <c r="B285" t="s">
+        <v>24</v>
+      </c>
+      <c r="C285" t="s">
+        <v>819</v>
+      </c>
+      <c r="D285" t="s">
+        <v>11</v>
+      </c>
+      <c r="E285" t="b">
+        <v>0</v>
+      </c>
+      <c r="F285" t="s">
+        <v>14</v>
+      </c>
+      <c r="G285">
+        <v>8</v>
+      </c>
+      <c r="H285" t="s">
+        <v>682</v>
+      </c>
+      <c r="I285" t="s">
+        <v>683</v>
+      </c>
+      <c r="J285">
+        <v>0</v>
+      </c>
+      <c r="K285">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="286" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A286" t="s">
+        <v>428</v>
+      </c>
+      <c r="B286" t="s">
+        <v>24</v>
+      </c>
+      <c r="C286" t="s">
+        <v>820</v>
+      </c>
+      <c r="D286" t="s">
+        <v>19</v>
+      </c>
+      <c r="E286" t="b">
+        <v>0</v>
+      </c>
+      <c r="F286" t="s">
+        <v>14</v>
+      </c>
+      <c r="G286">
+        <v>8</v>
+      </c>
+      <c r="H286" t="s">
+        <v>682</v>
+      </c>
+      <c r="I286" t="s">
+        <v>683</v>
+      </c>
+      <c r="J286">
+        <v>0</v>
+      </c>
+      <c r="K286">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="287" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A287" t="s">
+        <v>396</v>
+      </c>
+      <c r="B287" t="s">
+        <v>24</v>
+      </c>
+      <c r="C287" t="s">
+        <v>821</v>
+      </c>
+      <c r="D287" t="s">
+        <v>13</v>
+      </c>
+      <c r="E287" t="b">
+        <v>0</v>
+      </c>
+      <c r="F287" t="s">
+        <v>14</v>
+      </c>
+      <c r="G287">
+        <v>8</v>
+      </c>
+      <c r="H287" t="s">
+        <v>682</v>
+      </c>
+      <c r="I287" t="s">
+        <v>683</v>
+      </c>
+      <c r="J287">
+        <v>0</v>
+      </c>
+      <c r="K287">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="288" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A288" t="s">
+        <v>29</v>
+      </c>
+      <c r="B288" t="s">
+        <v>13</v>
+      </c>
+      <c r="C288" t="s">
+        <v>822</v>
+      </c>
+      <c r="D288" t="s">
+        <v>11</v>
+      </c>
+      <c r="E288" t="b">
+        <v>0</v>
+      </c>
+      <c r="F288" t="s">
+        <v>14</v>
+      </c>
+      <c r="G288">
+        <v>8</v>
+      </c>
+      <c r="H288" t="s">
+        <v>682</v>
+      </c>
+      <c r="I288" t="s">
+        <v>683</v>
+      </c>
+      <c r="J288">
+        <v>0</v>
+      </c>
+      <c r="K288">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="289" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A289" t="s">
+        <v>368</v>
+      </c>
+      <c r="B289" t="s">
+        <v>24</v>
+      </c>
+      <c r="C289" t="s">
+        <v>823</v>
+      </c>
+      <c r="D289" t="s">
+        <v>11</v>
+      </c>
+      <c r="E289" t="b">
+        <v>0</v>
+      </c>
+      <c r="F289" t="s">
+        <v>14</v>
+      </c>
+      <c r="G289">
+        <v>8</v>
+      </c>
+      <c r="H289" t="s">
+        <v>682</v>
+      </c>
+      <c r="I289" t="s">
+        <v>683</v>
+      </c>
+      <c r="J289">
+        <v>0</v>
+      </c>
+      <c r="K289">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="290" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A290" t="s">
+        <v>110</v>
+      </c>
+      <c r="B290" t="s">
+        <v>24</v>
+      </c>
+      <c r="C290" t="s">
+        <v>824</v>
+      </c>
+      <c r="D290" t="s">
+        <v>11</v>
+      </c>
+      <c r="E290" t="b">
+        <v>0</v>
+      </c>
+      <c r="F290" t="s">
+        <v>14</v>
+      </c>
+      <c r="G290">
+        <v>8</v>
+      </c>
+      <c r="H290" t="s">
+        <v>682</v>
+      </c>
+      <c r="I290" t="s">
+        <v>683</v>
+      </c>
+      <c r="J290">
+        <v>0</v>
+      </c>
+      <c r="K290">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="291" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A291" t="s">
+        <v>27</v>
+      </c>
+      <c r="B291" t="s">
+        <v>19</v>
+      </c>
+      <c r="C291" t="s">
+        <v>828</v>
+      </c>
+      <c r="D291" t="s">
+        <v>11</v>
+      </c>
+      <c r="E291" t="b">
+        <v>0</v>
+      </c>
+      <c r="F291" t="s">
+        <v>14</v>
+      </c>
+      <c r="G291">
+        <v>8</v>
+      </c>
+      <c r="H291" t="s">
+        <v>682</v>
+      </c>
+      <c r="I291" t="s">
+        <v>683</v>
+      </c>
+      <c r="J291">
+        <v>0</v>
+      </c>
+      <c r="K291">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="292" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A292" t="s">
+        <v>365</v>
+      </c>
+      <c r="B292" t="s">
+        <v>24</v>
+      </c>
+      <c r="C292" t="s">
+        <v>829</v>
+      </c>
+      <c r="D292" t="s">
+        <v>19</v>
+      </c>
+      <c r="E292" t="b">
+        <v>0</v>
+      </c>
+      <c r="F292" t="s">
+        <v>14</v>
+      </c>
+      <c r="G292">
+        <v>8</v>
+      </c>
+      <c r="H292" t="s">
+        <v>682</v>
+      </c>
+      <c r="I292" t="s">
+        <v>683</v>
+      </c>
+      <c r="J292">
+        <v>0</v>
+      </c>
+      <c r="K292">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="293" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A293" t="s">
+        <v>350</v>
+      </c>
+      <c r="B293" t="s">
+        <v>24</v>
+      </c>
+      <c r="C293" t="s">
+        <v>830</v>
+      </c>
+      <c r="D293" t="s">
+        <v>19</v>
+      </c>
+      <c r="E293" t="b">
+        <v>0</v>
+      </c>
+      <c r="F293" t="s">
+        <v>14</v>
+      </c>
+      <c r="G293">
+        <v>8</v>
+      </c>
+      <c r="H293" t="s">
+        <v>682</v>
+      </c>
+      <c r="I293" t="s">
+        <v>683</v>
+      </c>
+      <c r="J293">
+        <v>0</v>
+      </c>
+      <c r="K293">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="294" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A294" t="s">
+        <v>587</v>
+      </c>
+      <c r="B294" t="s">
+        <v>19</v>
+      </c>
+      <c r="C294" t="s">
+        <v>984</v>
+      </c>
+      <c r="D294" t="s">
+        <v>13</v>
+      </c>
+      <c r="E294" t="b">
+        <v>0</v>
+      </c>
+      <c r="F294" t="s">
+        <v>44</v>
+      </c>
+      <c r="G294">
+        <v>8</v>
+      </c>
+      <c r="H294" t="s">
+        <v>682</v>
+      </c>
+      <c r="I294" t="s">
+        <v>683</v>
+      </c>
+      <c r="J294">
+        <v>0</v>
+      </c>
+      <c r="K294">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="295" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A295" t="s">
+        <v>649</v>
+      </c>
+      <c r="B295" t="s">
+        <v>19</v>
+      </c>
+      <c r="C295" t="s">
+        <v>985</v>
+      </c>
+      <c r="D295" t="s">
+        <v>24</v>
+      </c>
+      <c r="E295" t="b">
+        <v>0</v>
+      </c>
+      <c r="F295" t="s">
+        <v>44</v>
+      </c>
+      <c r="G295">
+        <v>8</v>
+      </c>
+      <c r="H295" t="s">
+        <v>682</v>
+      </c>
+      <c r="I295" t="s">
+        <v>683</v>
+      </c>
+      <c r="J295">
+        <v>0</v>
+      </c>
+      <c r="K295">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="296" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A296" t="s">
+        <v>92</v>
+      </c>
+      <c r="B296" t="s">
+        <v>19</v>
+      </c>
+      <c r="C296" t="s">
+        <v>986</v>
+      </c>
+      <c r="D296" t="s">
+        <v>13</v>
+      </c>
+      <c r="E296" t="b">
+        <v>0</v>
+      </c>
+      <c r="F296" t="s">
+        <v>44</v>
+      </c>
+      <c r="G296">
+        <v>8</v>
+      </c>
+      <c r="H296" t="s">
+        <v>682</v>
+      </c>
+      <c r="I296" t="s">
+        <v>683</v>
+      </c>
+      <c r="J296">
+        <v>0</v>
+      </c>
+      <c r="K296">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="297" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A297" t="s">
+        <v>65</v>
+      </c>
+      <c r="B297" t="s">
+        <v>11</v>
+      </c>
+      <c r="C297" t="s">
+        <v>987</v>
+      </c>
+      <c r="D297" t="s">
+        <v>13</v>
+      </c>
+      <c r="E297" t="b">
+        <v>0</v>
+      </c>
+      <c r="F297" t="s">
+        <v>44</v>
+      </c>
+      <c r="G297">
+        <v>8</v>
+      </c>
+      <c r="H297" t="s">
+        <v>682</v>
+      </c>
+      <c r="I297" t="s">
+        <v>683</v>
+      </c>
+      <c r="J297">
+        <v>0</v>
+      </c>
+      <c r="K297">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="298" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A298" t="s">
+        <v>67</v>
+      </c>
+      <c r="B298" t="s">
+        <v>19</v>
+      </c>
+      <c r="C298" t="s">
+        <v>988</v>
+      </c>
+      <c r="D298" t="s">
+        <v>13</v>
+      </c>
+      <c r="E298" t="b">
+        <v>0</v>
+      </c>
+      <c r="F298" t="s">
+        <v>44</v>
+      </c>
+      <c r="G298">
+        <v>8</v>
+      </c>
+      <c r="H298" t="s">
+        <v>682</v>
+      </c>
+      <c r="I298" t="s">
+        <v>683</v>
+      </c>
+      <c r="J298">
+        <v>0</v>
+      </c>
+      <c r="K298">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="299" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A299" t="s">
+        <v>51</v>
+      </c>
+      <c r="B299" t="s">
+        <v>11</v>
+      </c>
+      <c r="C299" t="s">
+        <v>989</v>
+      </c>
+      <c r="D299" t="s">
+        <v>13</v>
+      </c>
+      <c r="E299" t="b">
+        <v>0</v>
+      </c>
+      <c r="F299" t="s">
+        <v>44</v>
+      </c>
+      <c r="G299">
+        <v>8</v>
+      </c>
+      <c r="H299" t="s">
+        <v>682</v>
+      </c>
+      <c r="I299" t="s">
+        <v>683</v>
+      </c>
+      <c r="J299">
+        <v>0</v>
+      </c>
+      <c r="K299">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="300" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A300" t="s">
+        <v>61</v>
+      </c>
+      <c r="B300" t="s">
+        <v>19</v>
+      </c>
+      <c r="C300" t="s">
+        <v>975</v>
+      </c>
+      <c r="D300" t="s">
+        <v>24</v>
+      </c>
+      <c r="E300" t="b">
+        <v>0</v>
+      </c>
+      <c r="F300" t="s">
+        <v>44</v>
+      </c>
+      <c r="G300">
+        <v>8</v>
+      </c>
+      <c r="H300" t="s">
+        <v>682</v>
+      </c>
+      <c r="I300" t="s">
+        <v>683</v>
+      </c>
+      <c r="J300">
+        <v>0</v>
+      </c>
+      <c r="K300">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="301" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A301" t="s">
+        <v>59</v>
+      </c>
+      <c r="B301" t="s">
+        <v>11</v>
+      </c>
+      <c r="C301" t="s">
+        <v>976</v>
+      </c>
+      <c r="D301" t="s">
+        <v>13</v>
+      </c>
+      <c r="E301" t="b">
+        <v>0</v>
+      </c>
+      <c r="F301" t="s">
+        <v>44</v>
+      </c>
+      <c r="G301">
+        <v>8</v>
+      </c>
+      <c r="H301" t="s">
+        <v>682</v>
+      </c>
+      <c r="I301" t="s">
+        <v>683</v>
+      </c>
+      <c r="J301">
+        <v>0</v>
+      </c>
+      <c r="K301">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="302" spans="1:11" x14ac:dyDescent="0.45">
+      <c r="A302" t="s">
+        <v>53</v>
+      </c>
+      <c r="B302" t="s">
+        <v>11</v>
+      </c>
+      <c r="C302" t="s">
+        <v>977</v>
+      </c>
+      <c r="D302" t="s">
+        <v>24</v>
+      </c>
+      <c r="E302" t="b">
+        <v>0</v>
+      </c>
+      <c r="F302" t="s">
+        <v>44</v>
+      </c>
+      <c r="G302">
+        <v>8</v>
+      </c>
+      <c r="H302" t="s">
+        <v>682</v>
+      </c>
+      <c r="I302" t="s">
+        <v>683</v>
+      </c>
+      <c r="J302">
+        <v>0</v>
+      </c>
+      <c r="K302">
         <v>0</v>
       </c>
     </row>
